--- a/Result/checksun/農業科技業.xlsx
+++ b/Result/checksun/農業科技業.xlsx
@@ -723,7 +723,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>弱勢突破股</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>352</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>352</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>352</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>352</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>352</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>352</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>352</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2819,12 +2819,12 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>352</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>352</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>352</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -3683,12 +3683,12 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>352</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>建議關注股</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3945,94 +3945,94 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>-0.67</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>-2.80</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>25.47</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>25.7475</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>26.489</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>-0.67</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>-1.08</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>-2.80</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>25.47</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>25.7475</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>26.489</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>-0.33</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>5.555555555555302</t>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>105.42</t>
+          <t>105.83</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>105.42</t>
+          <t>105.83</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>105.42</t>
+          <t>105.83</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>105.42</t>
+          <t>105.83</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>105.42</t>
+          <t>105.83</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>105.42</t>
+          <t>105.83</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>105.42</t>
+          <t>105.83</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>105.42</t>
+          <t>105.83</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>105.42</t>
+          <t>105.83</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>105.42</t>
+          <t>105.83</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>105.42</t>
+          <t>105.83</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
@@ -7067,7 +7067,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>多頭排列股</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7147,12 +7147,12 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
@@ -8587,12 +8587,12 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
@@ -8875,12 +8875,12 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -9626,7 +9626,7 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
@@ -9739,12 +9739,12 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -10202,7 +10202,7 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
@@ -10239,7 +10239,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>弱勢突破股</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -10289,24 +10289,24 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t>-0.17</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="O35" t="inlineStr">
         <is>
           <t>-1.0</t>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -10469,7 +10469,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -10479,7 +10479,7 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
@@ -10494,12 +10494,12 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
@@ -10577,7 +10577,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -10607,12 +10607,12 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -10782,12 +10782,12 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -10895,12 +10895,12 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
@@ -11070,12 +11070,12 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
@@ -11153,7 +11153,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -11183,12 +11183,12 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -11343,7 +11343,7 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -11358,12 +11358,12 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -11471,12 +11471,12 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -11646,12 +11646,12 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
@@ -11729,7 +11729,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -11759,12 +11759,12 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -11909,7 +11909,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>-9.48</t>
+          <t>-9.67</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -12197,7 +12197,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
@@ -12305,7 +12305,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-8.5</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -12335,12 +12335,12 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -12485,7 +12485,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-9.17</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -12623,12 +12623,12 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -12783,7 +12783,7 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
@@ -12798,12 +12798,12 @@
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-8.5</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -12911,12 +12911,12 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -13071,7 +13071,7 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -13086,12 +13086,12 @@
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
@@ -13169,7 +13169,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>-8.65</t>
+          <t>-8.83</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -13199,12 +13199,12 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
@@ -13374,12 +13374,12 @@
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">

--- a/Result/checksun/農業科技業.xlsx
+++ b/Result/checksun/農業科技業.xlsx
@@ -1013,7 +1013,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -1301,7 +1305,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -1589,7 +1597,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -1877,7 +1889,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -2165,7 +2181,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -2453,7 +2473,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -2741,7 +2765,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -3029,7 +3057,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -3317,7 +3349,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -3605,7 +3641,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -4185,7 +4225,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -4473,7 +4517,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -4761,7 +4809,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -5049,7 +5101,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -5337,7 +5393,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -5625,7 +5685,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -5913,7 +5977,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -6201,7 +6269,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -6489,7 +6561,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -6777,7 +6853,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -7645,7 +7725,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -7933,7 +8017,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -8221,7 +8309,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -8509,7 +8601,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -8797,7 +8893,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -9085,7 +9185,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -9373,7 +9477,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -9661,7 +9769,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -9949,7 +10061,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -10237,7 +10353,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>2025-08-25</t>

--- a/Result/checksun/農業科技業.xlsx
+++ b/Result/checksun/農業科技業.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -738,44 +738,44 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>286.0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>22.68</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-2.43</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>22.65</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>0.22</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>236.0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>18.72</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>-0.43</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>22.7</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>0</t>
@@ -783,22 +783,22 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>71</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-13.0</t>
+          <t>-19.0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -813,62 +813,62 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.81</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>23.9475</t>
+          <t>23.885</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>23.161</t>
+          <t>23.215</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>-232.18</t>
+          <t>-461.19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>6.97674418604645</t>
+          <t>10.52631578947347</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>3.875968992247981</t>
+          <t>7.38474092207247</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>201.20</t>
+          <t>152.19</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -878,27 +878,27 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>1674.4</t>
+          <t>948.8</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-1654.6</t>
+          <t>-1818.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-201</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-464.4737104806295</t>
+          <t>-392.2924199731914</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>578.57</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>381.0</t>
+          <t>236.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1045,17 +1045,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>30.21</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1075,22 +1075,22 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>90</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>-13.0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -1105,62 +1105,62 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>22.98</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.9475</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>23.101</t>
+          <t>23.161</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-156.43</t>
+          <t>-232.18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>4.651162790697579</t>
+          <t>6.97674418604645</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>9.88372093023248</t>
+          <t>3.875968992247981</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>201.20</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1170,27 +1170,27 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-1585.0</t>
+          <t>1674.4</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>-1778.2</t>
+          <t>-1654.6</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-654.1174894962272</t>
+          <t>-464.4737104806295</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>101.42</t>
+          <t>578.57</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1215,12 +1215,12 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>528.0</t>
+          <t>381.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1337,17 +1337,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>30.21</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1367,22 +1367,22 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>103</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1397,62 +1397,62 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-3.80</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>22.98</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>24.0025</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>23.041</t>
+          <t>23.101</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-113.04</t>
+          <t>-156.43</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.651162790697579</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>8.333333333333286</t>
+          <t>9.88372093023248</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-29.89</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1462,27 +1462,27 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-4878.8</t>
+          <t>-1585.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>-3756.1</t>
+          <t>-1778.2</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>193</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-791.4882463678586</t>
+          <t>-654.1174894962272</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-937.52</t>
+          <t>101.42</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>393.0</t>
+          <t>528.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1659,17 +1659,17 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>83</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1689,52 +1689,52 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-3.80</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>23.27</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>24.0875</t>
+          <t>24.0025</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>22.983</t>
+          <t>23.041</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-79.56</t>
+          <t>-113.04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>24.99999999999994</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-52.78</t>
+          <t>-29.89</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1754,27 +1754,27 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-4828.0</t>
+          <t>-4878.8</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>-3160.1</t>
+          <t>-3756.1</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-1122</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-764.9378570499535</t>
+          <t>-791.4882463678586</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-173.37</t>
+          <t>-937.52</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>393.0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1951,24 +1951,24 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>78</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>-30.0</t>
-        </is>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>0</t>
@@ -1981,62 +1981,62 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>23.27</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>24.14</t>
+          <t>24.0875</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>22.906</t>
+          <t>22.983</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-74.95</t>
+          <t>-79.56</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.99999999999994</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.333333333333286</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-43.63</t>
+          <t>-52.78</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2046,27 +2046,27 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-4584.8</t>
+          <t>-4828.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>-3192.1</t>
+          <t>-3160.1</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-1667</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-872.4954031226443</t>
+          <t>-764.9378570499535</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1346.12</t>
+          <t>-173.37</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2091,12 +2091,12 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>468.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2243,22 +2243,22 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>73</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>-30.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -2273,47 +2273,47 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>23.68</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>24.2625</t>
+          <t>24.14</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>22.834</t>
+          <t>22.906</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-61.97</t>
+          <t>-74.95</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-43.91</t>
+          <t>-43.63</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -2338,27 +2338,27 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-4983.6</t>
+          <t>-4584.8</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-3463.0</t>
+          <t>-3192.1</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-1392</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-786.3824557039895</t>
+          <t>-872.4954031226443</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1676.43</t>
+          <t>-1346.12</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2383,12 +2383,12 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>333.0</t>
+          <t>468.0</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2505,17 +2505,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>26.41</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2535,22 +2535,22 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>103</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -2565,47 +2565,47 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>23.88</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>24.2625</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>22.765</t>
+          <t>22.834</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>-48.85</t>
+          <t>-61.97</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -2615,12 +2615,12 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>19.04761904761902</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>32.83</t>
+          <t>-43.91</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -2630,27 +2630,27 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-1971.4</t>
+          <t>-4983.6</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-2934.8</t>
+          <t>-3463.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-32</t>
+          <t>-1520</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-624.5561555268883</t>
+          <t>-786.3824557039895</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1229.89</t>
+          <t>-1676.43</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2782,12 +2782,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>503.0</t>
+          <t>333.0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2797,17 +2797,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>39.89</t>
+          <t>26.41</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2827,22 +2827,22 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>99</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -2857,47 +2857,47 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>7.54</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>23.88</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>22.69</t>
+          <t>22.765</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>-36.01</t>
+          <t>-48.85</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>23.80952380952378</t>
+          <t>19.04761904761902</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-107.34</t>
+          <t>32.83</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -2922,27 +2922,27 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-2633.4</t>
+          <t>-1971.4</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>-1270.1</t>
+          <t>-2934.8</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>963</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-514.4952513991846</t>
+          <t>-624.5561555268883</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-883.31</t>
+          <t>-1229.89</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2967,12 +2967,12 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>418.0</t>
+          <t>503.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3089,17 +3089,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>39.89</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-8.81</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -3119,22 +3119,22 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>89</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -3149,62 +3149,62 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>23.98</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>24.42</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>22.615</t>
+          <t>22.69</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>-24.42</t>
+          <t>-36.01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>57.14285714285714</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>31.42857142857144</t>
+          <t>23.80952380952378</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-300.56</t>
+          <t>-107.34</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -3214,27 +3214,27 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-1492.2</t>
+          <t>-2633.4</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>744.0</t>
+          <t>-1270.1</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-300</t>
+          <t>-1363</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-447.4384053922925</t>
+          <t>-514.4952513991846</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>66.46</t>
+          <t>-883.31</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>418.0</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3381,17 +3381,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-8.81</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -3441,62 +3441,62 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>24.355</t>
+          <t>24.42</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>22.506</t>
+          <t>22.615</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>-27.50</t>
+          <t>-24.42</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14.28571428571428</t>
+          <t>57.14285714285714</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>12.38095238095239</t>
+          <t>31.42857142857144</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-149850.00</t>
+          <t>-300.56</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -3506,27 +3506,27 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-1799.4</t>
+          <t>-1492.2</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>744.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>149850</t>
+          <t>-2236</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-540.8753591771593</t>
+          <t>-447.4384053922925</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-952.73</t>
+          <t>66.46</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>207.0</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3673,17 +3673,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>13.72</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-6.17</t>
+          <t>-5.51</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -3733,62 +3733,62 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>24.63</t>
+          <t>24.44</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>24.3125</t>
+          <t>24.355</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>22.411</t>
+          <t>22.506</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>-21.53</t>
+          <t>-27.50</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>22.85714285714298</t>
+          <t>14.28571428571428</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>35.39682539682541</t>
+          <t>12.38095238095239</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>-348.17</t>
+          <t>-149850.00</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -3798,27 +3798,27 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>-1942.4</t>
+          <t>-1799.4</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>782.7</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-348</t>
+          <t>-1798</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-465.9920510140678</t>
+          <t>-540.8753591771593</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-733.81</t>
+          <t>-952.73</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -3935,12 +3935,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -3985,32 +3985,32 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>-13.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -4025,62 +4025,62 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>24.985</t>
+          <t>24.93</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>25.813</t>
+          <t>25.767</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>20.00000000000028</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>6.666666666666771</t>
+          <t>23.33333333333344</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>63.37</t>
+          <t>-9.91</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -4090,27 +4090,27 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>-420.6</t>
+          <t>-423.8</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>-1148.2</t>
+          <t>-385.6</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-63</t>
+          <t>-38</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-39.77877162149947</t>
+          <t>-9.512021718183899</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>156.96</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -4257,122 +4257,122 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>15.57</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>24.45</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>-13.0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>-2.02</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>-3.21</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>24.48</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>24.985</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>25.813</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>-2.04</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>-0.41</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>24.4</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>-0.41</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>-2.17</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>-3.15</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>24.5</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>25.0425</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>25.858</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>-4.87</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>-0.42</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.00000000000028</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.666666666666771</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>43.02</t>
+          <t>63.37</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -4382,27 +4382,27 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>-715.8</t>
+          <t>-420.6</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>-1256.3</t>
+          <t>-1148.2</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-43</t>
+          <t>727</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-61.44674194549375</t>
+          <t>-39.77877162149947</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-26.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -4427,12 +4427,12 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4549,17 +4549,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>15.57</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -4569,102 +4569,102 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>-2.17</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>-3.15</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>24.5</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>25.0425</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>25.858</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>-4.87</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>-0.42</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>-0.40</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>-6.0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>-0.33</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>-2.28</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>-3.11</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>24.53</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>25.1025</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>25.907</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>-6.31</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>-0.42</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2.083333333333371</t>
-        </is>
-      </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>45.58</t>
+          <t>43.02</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
@@ -4674,27 +4674,27 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>-676.6</t>
+          <t>-715.8</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>-1243.3</t>
+          <t>-1256.3</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-45</t>
+          <t>540</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-67.83488499889101</t>
+          <t>-61.44674194549375</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-9.78</t>
+          <t>-26.31</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4719,12 +4719,12 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4841,17 +4841,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>19.38</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>35</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -4901,37 +4901,37 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>25.16</t>
+          <t>25.1025</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>25.954</t>
+          <t>25.907</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-6.31</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>45.58</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
@@ -4966,27 +4966,27 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>-941.6</t>
+          <t>-676.6</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>-1198.4</t>
+          <t>-1243.3</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-21</t>
+          <t>566</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-78.39120433901441</t>
+          <t>-67.83488499889101</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-36.69</t>
+          <t>-9.78</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -5133,17 +5133,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>19.38</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>41</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>-20.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -5193,37 +5193,37 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>24.59</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>25.2175</t>
+          <t>25.16</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>25.999</t>
+          <t>25.954</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>-9.74</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>6.250000000000083</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>66.15</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
@@ -5258,27 +5258,27 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>-347.4</t>
+          <t>-941.6</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>-1026.4</t>
+          <t>-1198.4</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-66</t>
+          <t>256</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-85.97236219274511</t>
+          <t>-78.39120433901441</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>-36.69</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -5303,12 +5303,12 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5410,67 +5410,67 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>7.61</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-0.61</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>14.53</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>24.55</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>-8.0</t>
+          <t>-20.0</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -5485,17 +5485,17 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -5505,17 +5505,17 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>25.2675</t>
+          <t>25.2175</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26.047</t>
+          <t>25.999</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>-13.06</t>
+          <t>-9.74</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -5530,17 +5530,17 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.250000000000083</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.083333333333371</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>-58.68</t>
+          <t>66.15</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
@@ -5550,27 +5550,27 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>-1875.8</t>
+          <t>-347.4</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>-1182.1</t>
+          <t>-1026.4</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-102.8468898869734</t>
+          <t>-85.97236219274511</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-137.25</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -5717,12 +5717,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>12.80</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -5752,17 +5752,17 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>54</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>-87.0</t>
+          <t>-8.0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -5777,37 +5777,37 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>24.74</t>
+          <t>24.59</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>25.3225</t>
+          <t>25.2675</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26.091</t>
+          <t>26.047</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>-14.54</t>
+          <t>-13.06</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2.083333333333232</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>-95.01</t>
+          <t>-58.68</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
@@ -5842,27 +5842,27 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>-1796.8</t>
+          <t>-1875.8</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>-921.4</t>
+          <t>-1182.1</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>-693</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-96.59118567258551</t>
+          <t>-102.8468898869734</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-170.41</t>
+          <t>-137.25</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -6009,17 +6009,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>27.34</t>
+          <t>12.80</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -6039,84 +6039,84 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>62</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>-87.0</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>-0.77</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>-2.30</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>-2.95</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>24.74</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>25.3225</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>26.091</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>-14.54</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>-0.42</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>-0.36</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>-1.20</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>-1.89</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>-2.92</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>25.38</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>26.144</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>-14.03</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
           <t>2.083333333333232</t>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>-97.62</t>
+          <t>-95.01</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
@@ -6134,27 +6134,27 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>-1810.0</t>
+          <t>-1796.8</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>-915.9</t>
+          <t>-921.4</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>-875</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-83.1696465062403</t>
+          <t>-96.59118567258551</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-224.23</t>
+          <t>-170.41</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -6179,12 +6179,12 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -6301,17 +6301,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>27.34</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>149</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -6361,52 +6361,52 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>25.435</t>
+          <t>25.38</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26.204</t>
+          <t>26.144</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>-11.58</t>
+          <t>-14.03</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>6.249999999999667</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>-78.29</t>
+          <t>-97.62</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
@@ -6426,27 +6426,27 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>-1455.2</t>
+          <t>-1810.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>-816.2</t>
+          <t>-915.9</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>-894</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-57.52311405141918</t>
+          <t>-83.1696465062403</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-181.03</t>
+          <t>-224.23</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>289.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -6593,17 +6593,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -6653,62 +6653,62 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>25.435</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26.264</t>
+          <t>26.204</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-11.58</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.249999999999667</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>4.761904761904868</t>
+          <t>2.083333333333232</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>-91.02</t>
+          <t>-78.29</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
@@ -6718,27 +6718,27 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>-1705.4</t>
+          <t>-1455.2</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>-892.8</t>
+          <t>-816.2</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>-639</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-35.06804724245443</t>
+          <t>-57.52311405141918</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-492.45</t>
+          <t>-181.03</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
@@ -6855,12 +6855,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>289.0</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -6885,17 +6885,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -6905,7 +6905,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -6945,47 +6945,47 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>25.34</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>25.545</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26.326</t>
+          <t>26.264</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -6995,12 +6995,12 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>9.523809523809726</t>
+          <t>4.761904761904868</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>-71.79</t>
+          <t>-91.02</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
@@ -7010,27 +7010,27 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>-488.4</t>
+          <t>-1705.4</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>-284.3</t>
+          <t>-892.8</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>-812</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>48.09307248124434</t>
+          <t>-35.06804724245443</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>11.31</t>
+          <t>-492.45</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -7162,29 +7162,29 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>61.0</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>-0.55</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>35.0</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>18.1</t>
@@ -7212,87 +7212,87 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>-0.39</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>-3.30</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>-3.60</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>18.17</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>18.79</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>19.492</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>-9.34</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>-0.42</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>-0.49</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>-3.63</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>-3.42</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>18.19</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>18.875</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>19.544</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>-13.06</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>-0.47</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>5.73870573870565</t>
+          <t>3.174603174603135</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>24.73</t>
+          <t>13.82</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
@@ -7302,27 +7302,27 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>-390.4</t>
+          <t>-487.2</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>-518.7</t>
+          <t>-565.3</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>-24</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>-26.5066568860711</t>
+          <t>-32.05454276520601</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-14.25</t>
+          <t>-62.57</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -7454,44 +7454,44 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>45.0</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>18.2</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>0</t>
@@ -7529,37 +7529,37 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>18.21</t>
+          <t>18.19</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>18.965</t>
+          <t>18.875</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>19.586</t>
+          <t>19.544</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>-16.63</t>
+          <t>-13.06</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -7569,22 +7569,22 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>9.523809523809348</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>9.584859584859467</t>
+          <t>5.73870573870565</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>71.36</t>
+          <t>24.73</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
@@ -7594,27 +7594,27 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>-149.6</t>
+          <t>-390.4</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>-522.3</t>
+          <t>-518.7</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>-71</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>-28.73552465984942</t>
+          <t>-26.5066568860711</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>-14.25</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -7746,12 +7746,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -7761,12 +7761,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -7821,37 +7821,37 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>18.21</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>18.965</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>19.624</t>
+          <t>19.586</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>-22.25</t>
+          <t>-16.63</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -7861,22 +7861,22 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>7.692307692307546</t>
+          <t>9.523809523809348</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>8.974358974358866</t>
+          <t>9.584859584859467</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>158.64</t>
+          <t>71.36</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
@@ -7886,27 +7886,27 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>307.4</t>
+          <t>-149.6</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>-524.2</t>
+          <t>-522.3</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>-158</t>
+          <t>372</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>-34.8374925674095</t>
+          <t>-28.73552465984942</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>51.29</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -8038,12 +8038,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -8053,17 +8053,17 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -8113,37 +8113,37 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>19.135</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>19.624</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>-28.33</t>
+          <t>-22.25</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -8153,22 +8153,22 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11.53846153846145</t>
+          <t>7.692307692307546</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>8.791208791208685</t>
+          <t>8.974358974358866</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>93.96</t>
+          <t>158.64</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
@@ -8178,27 +8178,27 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>-32.0</t>
+          <t>307.4</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>-530.2</t>
+          <t>-524.2</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>-93</t>
+          <t>831</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>-50.49762359874104</t>
+          <t>-34.8374925674095</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>87.24</t>
+          <t>51.29</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -8330,67 +8330,67 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>18.25</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>-0.83</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>34.0</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>0.81</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>18.2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -8405,62 +8405,62 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>18.24</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>19.22</t>
+          <t>19.135</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.66</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>-36.05</t>
+          <t>-28.33</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>7.692307692307546</t>
+          <t>11.53846153846145</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>6.135531135530992</t>
+          <t>8.791208791208685</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>93.96</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
@@ -8470,27 +8470,27 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>-643.4</t>
+          <t>-32.0</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>-668.6</t>
+          <t>-530.2</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>498</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>-75.54027158916146</t>
+          <t>-50.49762359874104</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>7.54</t>
+          <t>87.24</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -8622,12 +8622,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -8667,17 +8667,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -8697,62 +8697,62 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>18.43</t>
+          <t>18.24</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>19.3275</t>
+          <t>19.22</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>19.739</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>-42.82</t>
+          <t>-36.05</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>7.142857142856998</t>
+          <t>7.692307692307546</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>3.571428571428476</t>
+          <t>6.135531135530992</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>-20.66</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
@@ -8762,27 +8762,27 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>-647.0</t>
+          <t>-643.4</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>-536.2</t>
+          <t>-668.6</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>-90.64594356094223</t>
+          <t>-75.54027158916146</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -8807,12 +8807,12 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -8959,22 +8959,22 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -8989,62 +8989,62 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>18.43</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>19.4325</t>
+          <t>19.3275</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>19.777</t>
+          <t>19.739</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>-48.03</t>
+          <t>-42.82</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>3.571428571428372</t>
+          <t>7.142857142856998</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>1.190476190476143</t>
+          <t>3.571428571428476</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>-82.02</t>
+          <t>-20.66</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
@@ -9054,27 +9054,27 @@
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>-895.0</t>
+          <t>-647.0</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>-491.7</t>
+          <t>-536.2</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>-112.4306885667275</t>
+          <t>-90.64594356094223</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-68.58</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -9206,12 +9206,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -9221,17 +9221,17 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -9251,22 +9251,22 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -9281,62 +9281,62 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>19.525</t>
+          <t>19.4325</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>19.81</t>
+          <t>19.777</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>-46.38</t>
+          <t>-48.03</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.571428571428372</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.190476190476143</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>-90.29</t>
+          <t>-82.02</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
@@ -9346,27 +9346,27 @@
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>-1355.8</t>
+          <t>-895.0</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>-712.5</t>
+          <t>-491.7</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>-403</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>-120.4035627595313</t>
+          <t>-112.4306885667275</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-302.2</t>
+          <t>-68.58</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -9513,17 +9513,17 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -9543,22 +9543,22 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -9573,47 +9573,47 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>19.6225</t>
+          <t>19.525</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>19.856</t>
+          <t>19.81</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>-29.25</t>
+          <t>-46.38</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -9623,12 +9623,12 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>19.99999999999983</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>-96.86</t>
+          <t>-90.29</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
@@ -9638,27 +9638,27 @@
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>-1028.4</t>
+          <t>-1355.8</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>-522.4</t>
+          <t>-712.5</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>-643</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>-87.34928746413703</t>
+          <t>-120.4035627595313</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>-227.12</t>
+          <t>-302.2</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -9805,17 +9805,17 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>-5.8</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -9865,47 +9865,47 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>19.37</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>19.695</t>
+          <t>19.6225</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>19.895</t>
+          <t>19.856</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>-10.56</t>
+          <t>-29.25</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>29.09090909090882</t>
+          <t>19.99999999999983</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>-85.21</t>
+          <t>-96.86</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
@@ -9930,27 +9930,27 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>-693.8</t>
+          <t>-1028.4</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>-374.6</t>
+          <t>-522.4</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>-506</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>-61.93653498366112</t>
+          <t>-87.34928746413703</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>-93.96</t>
+          <t>-227.12</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -10072,7 +10072,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -10082,137 +10082,137 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>-1.29</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>33.0</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-1.31</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>19.15</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>-5.8</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>-1.65</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>19.37</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>19.695</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>19.895</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>-10.56</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>-0.20</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>34.0</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>0.81</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>19.4</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>-7.18</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>-1.46</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>-1.01</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>19.44</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>19.7275</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>19.928</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>-5.77</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>59.99999999999943</t>
-        </is>
-      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>36.78321678321646</t>
+          <t>29.09090909090882</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-85.21</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
@@ -10222,27 +10222,27 @@
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>-425.4</t>
+          <t>-693.8</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>-423.0</t>
+          <t>-374.6</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-319</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>-56.11383696910235</t>
+          <t>-61.93653498366112</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>-90.24</t>
+          <t>-93.96</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -10292,7 +10292,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -10364,7 +10364,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -10374,129 +10374,129 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>57.8</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>-2.02</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>-3.38</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>58.08</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>59.275</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>61.348</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>-9.35</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>-1.12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>-1.02</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>0.20</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>58.0</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>-1.80</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>-3.40</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>59.37</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>61.458</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>-12.08</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>-1.12</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>-1.00</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11.76470588235309</t>
-        </is>
-      </c>
       <c r="AC35" t="inlineStr">
         <is>
           <t>6.951871657754103</t>
@@ -10504,7 +10504,7 @@
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>-19.85</t>
+          <t>-12.85</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr">
@@ -10514,27 +10514,27 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>-685.8</t>
+          <t>-942.4</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>-572.2</t>
+          <t>-835.1</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-107</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>-149.4022929674022</t>
+          <t>-142.9106285822114</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>-82.26</t>
+          <t>-107.21</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -10559,7 +10559,7 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -10721,7 +10721,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -10761,17 +10761,17 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>59.76000000000001</t>
+          <t>59.37</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>61.57</t>
+          <t>61.458</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>-16.13</t>
+          <t>-12.08</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -10781,22 +10781,22 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>9.090909090909207</t>
+          <t>11.76470588235309</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>16.36363636363636</t>
+          <t>6.951871657754103</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>11.92</t>
+          <t>-19.85</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr">
@@ -10806,27 +10806,27 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>-625.0</t>
+          <t>-685.8</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>-709.6</t>
+          <t>-572.2</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-113</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>-161.6107228148097</t>
+          <t>-149.4022929674022</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>-111.92</t>
+          <t>-82.26</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
@@ -10948,7 +10948,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -10958,12 +10958,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -10973,17 +10973,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -10993,7 +10993,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -11033,62 +11033,62 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>58.31999999999999</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>60.11499999999999</t>
+          <t>59.76000000000001</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>61.68</t>
+          <t>61.57</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>-20.00</t>
+          <t>-16.13</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.090909090909207</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>26.37681159420285</t>
+          <t>16.36363636363636</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>11.92</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr">
@@ -11098,27 +11098,27 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>-996.2</t>
+          <t>-625.0</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>-905.0</t>
+          <t>-709.6</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>-170.6445668882826</t>
+          <t>-161.6107228148097</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>-332.35</t>
+          <t>-111.92</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -11265,17 +11265,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -11295,84 +11295,84 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>-0.89</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>-2.99</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>-2.54</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>58.31999999999999</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>60.11499999999999</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>61.68</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>-20.00</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>-1.11</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>-0.93</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>-3.47</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>-2.09</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>58.4</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>60.5</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>61.794</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>-20.81</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>-0.88</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>39.99999999999986</t>
-        </is>
-      </c>
       <c r="AC38" t="inlineStr">
         <is>
           <t>26.37681159420285</t>
@@ -11380,7 +11380,7 @@
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>-45.93</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr">
@@ -11390,27 +11390,27 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>-722.8</t>
+          <t>-996.2</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>-495.3</t>
+          <t>-905.0</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-91</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>-141.2441651845223</t>
+          <t>-170.6445668882826</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>-94.83</t>
+          <t>-332.35</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
@@ -11460,7 +11460,7 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AU38" t="inlineStr">
@@ -11532,7 +11532,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -11542,12 +11542,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -11557,17 +11557,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -11597,12 +11597,12 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -11617,62 +11617,62 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>58.54</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>60.815</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>61.892</t>
+          <t>61.794</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>-30.35</t>
+          <t>-20.81</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>39.13043478260868</t>
+          <t>39.99999999999986</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>13.04347826086956</t>
+          <t>26.37681159420285</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>-44.00</t>
+          <t>-45.93</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr">
@@ -11682,27 +11682,27 @@
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>-727.8</t>
+          <t>-722.8</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>-505.4</t>
+          <t>-495.3</t>
         </is>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-227</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>-149.68303422507</t>
+          <t>-141.2441651845223</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>-84.6</t>
+          <t>-94.83</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -11727,12 +11727,12 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -11849,17 +11849,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -11879,29 +11879,29 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R40" t="inlineStr">
         <is>
           <t>8</t>
@@ -11909,62 +11909,62 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>58.76000000000001</t>
+          <t>58.54</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>61.13500000000001</t>
+          <t>60.815</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>61.974</t>
+          <t>61.892</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>-44.34</t>
+          <t>-30.35</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.13043478260868</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.04347826086956</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>21.22</t>
+          <t>-44.00</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr">
@@ -11974,27 +11974,27 @@
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>-458.6</t>
+          <t>-727.8</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>-582.1</t>
+          <t>-505.4</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>-21</t>
+          <t>-222</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>-161.5165419051957</t>
+          <t>-149.68303422507</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>-162.21</t>
+          <t>-84.6</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -12019,12 +12019,12 @@
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="AQ40" t="inlineStr">
@@ -12044,7 +12044,7 @@
       </c>
       <c r="AT40" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AU40" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -12141,17 +12141,17 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -12161,7 +12161,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -12171,7 +12171,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -12201,47 +12201,47 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>58.76000000000001</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>61.42</t>
+          <t>61.13500000000001</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>62.06</t>
+          <t>61.974</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>-51.36</t>
+          <t>-44.34</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -12256,7 +12256,7 @@
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>-18.38</t>
+          <t>21.22</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr">
@@ -12266,27 +12266,27 @@
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>-794.2</t>
+          <t>-458.6</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>-670.9</t>
+          <t>-582.1</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>-161.3903268328094</t>
+          <t>-161.5165419051957</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>-230.65</t>
+          <t>-162.21</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -12311,7 +12311,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AU41" t="inlineStr">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -12418,12 +12418,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -12433,17 +12433,17 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -12453,7 +12453,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -12463,22 +12463,22 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -12493,47 +12493,47 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>59.52</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>61.74499999999999</t>
+          <t>61.42</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>62.14</t>
+          <t>62.06</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>-56.76</t>
+          <t>-51.36</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -12543,12 +12543,12 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>4.761904761904815</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>-26.39</t>
+          <t>-18.38</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr">
@@ -12558,27 +12558,27 @@
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>-813.8</t>
+          <t>-794.2</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>-643.9</t>
+          <t>-670.9</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-123</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>-148.7978610462598</t>
+          <t>-161.3903268328094</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>-270.79</t>
+          <t>-230.65</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -12725,17 +12725,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -12745,7 +12745,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -12755,84 +12755,84 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>-2.22</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>-3.60</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>-0.64</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>59.52</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>61.74499999999999</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>62.14</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>-56.76</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>-0.94</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>-0.60</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>-0.73</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>-3.38</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>59.94</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>62.04000000000001</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>62.21</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>-56.86</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>-0.81</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AC43" t="inlineStr">
         <is>
           <t>4.761904761904815</t>
@@ -12840,7 +12840,7 @@
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>8.91</t>
+          <t>-26.39</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr">
@@ -12850,27 +12850,27 @@
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>-267.8</t>
+          <t>-813.8</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>-294.0</t>
+          <t>-643.9</t>
         </is>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-169</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>-126.6179491065604</t>
+          <t>-148.7978610462598</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>-123.24</t>
+          <t>-270.79</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -12920,7 +12920,7 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AU43" t="inlineStr">
@@ -12987,12 +12987,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -13002,12 +13002,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -13017,17 +13017,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -13037,7 +13037,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -13077,62 +13077,62 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>60.04</t>
+          <t>59.94</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>62.26000000000001</t>
+          <t>62.04000000000001</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>62.26</t>
+          <t>62.21</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>-71.81</t>
+          <t>-56.86</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14.28571428571443</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>15.87301587301584</t>
+          <t>4.761904761904815</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>-142.50</t>
+          <t>8.91</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr">
@@ -13142,27 +13142,27 @@
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>-283.0</t>
+          <t>-267.8</t>
         </is>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>-116.7</t>
+          <t>-294.0</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>-127.231610674472</t>
+          <t>-126.6179491065604</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>-91.38</t>
+          <t>-123.24</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -13187,7 +13187,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
@@ -13212,7 +13212,7 @@
       </c>
       <c r="AT44" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AU44" t="inlineStr">
@@ -13284,7 +13284,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -13294,12 +13294,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -13309,122 +13309,122 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>-3.45</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>-3.57</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>59.9</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>-3.28</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>-3.78</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>60.06</t>
+          <t>60.04</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>62.42</t>
+          <t>62.26000000000001</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>62.3</t>
+          <t>62.26</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>-103.26</t>
+          <t>-71.81</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.28571428571443</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>14.38979963570116</t>
+          <t>15.87301587301584</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>-142.50</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr">
@@ -13434,27 +13434,27 @@
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>-705.6</t>
+          <t>-283.0</t>
         </is>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>-895.9</t>
+          <t>-116.7</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>-21</t>
+          <t>-166</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>-133.7492201881431</t>
+          <t>-127.231610674472</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>-284.75</t>
+          <t>-91.38</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -13479,7 +13479,7 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">

--- a/Result/checksun/農業科技業.xlsx
+++ b/Result/checksun/農業科技業.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF41"/>
+  <dimension ref="A1:BF40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -728,7 +728,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>392.0</t>
+          <t>437.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -753,17 +753,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>31.09</t>
+          <t>34.66</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -783,17 +783,17 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -803,57 +803,57 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>437</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-6.49</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>23.6025</t>
+          <t>23.3875</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>23.26899999999999</t>
+          <t>23.276</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>-362.37</t>
+          <t>-201.99</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -863,12 +863,12 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>3.50877192982446</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>-54.59</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -878,27 +878,27 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-1854.0</t>
+          <t>-5395.6</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-3366.4</t>
+          <t>-3490.3</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>-1905</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-489.9874388550896</t>
+          <t>-596.6561364035385</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-902.65</t>
+          <t>-1183.33</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>380.0</t>
+          <t>392.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1045,122 +1045,122 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>31.09</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>-1.2</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>-7</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>-6.0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>-5.62</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>-5.73</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
           <t>22.25</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>-5.95</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>23.6025</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>23.26899999999999</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>-362.37</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>-0.09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>392</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>-1.37</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>-5.20</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>22.56</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>23.7975</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>23.254</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>-3048.39</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>5.834353325173278</t>
+          <t>3.50877192982446</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>30.38</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1170,27 +1170,27 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-2577.8</t>
+          <t>-1854.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>-3702.9</t>
+          <t>-3366.4</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-414.9576809817669</t>
+          <t>-489.9874388550896</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-539.62</t>
+          <t>-902.65</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1215,12 +1215,12 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>286.0</t>
+          <t>380.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1337,17 +1337,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22.68</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-7.86</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1377,82 +1377,82 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-19.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>437</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-5.20</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>22.81</t>
+          <t>22.56</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>23.885</t>
+          <t>23.7975</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>23.215</t>
+          <t>23.254</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-461.19</t>
+          <t>-3048.39</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10.52631578947347</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>7.38474092207247</t>
+          <t>5.834353325173278</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>152.19</t>
+          <t>30.38</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1462,27 +1462,27 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>948.8</t>
+          <t>-2577.8</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>-1818.0</t>
+          <t>-3702.9</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2766</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-392.2924199731914</t>
+          <t>-414.9576809817669</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>-539.62</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1507,12 +1507,12 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>236.0</t>
+          <t>286.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>22.68</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-8.1</t>
+          <t>-9.16</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1659,92 +1659,92 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>71</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-13.0</t>
+          <t>-19.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>437</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.81</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>23.9475</t>
+          <t>23.885</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>23.161</t>
+          <t>23.215</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-232.18</t>
+          <t>-461.19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>6.97674418604645</t>
+          <t>10.52631578947347</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>3.875968992247981</t>
+          <t>7.38474092207247</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>201.20</t>
+          <t>152.19</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1754,27 +1754,27 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>1674.4</t>
+          <t>948.8</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>-1654.6</t>
+          <t>-1818.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>3329</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-464.4737104806295</t>
+          <t>-392.2924199731914</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>578.57</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>381.0</t>
+          <t>236.0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>30.21</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-7.86</t>
+          <t>-9.4</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1951,92 +1951,92 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>90</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>-13.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>437</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>22.98</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.9475</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>23.101</t>
+          <t>23.161</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-156.43</t>
+          <t>-232.18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>4.651162790697579</t>
+          <t>6.97674418604645</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>9.88372093023248</t>
+          <t>3.875968992247981</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>201.20</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2046,27 +2046,27 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-1585.0</t>
+          <t>1674.4</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>-1778.2</t>
+          <t>-1654.6</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-654.1174894962272</t>
+          <t>-464.4737104806295</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>101.42</t>
+          <t>578.57</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2091,12 +2091,12 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>528.0</t>
+          <t>381.0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2213,17 +2213,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>30.21</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-7.38</t>
+          <t>-9.16</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2243,92 +2243,92 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>103</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>437</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>-3.80</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>22.98</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>24.0025</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>23.041</t>
+          <t>23.101</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-113.04</t>
+          <t>-156.43</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.651162790697579</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>8.333333333333286</t>
+          <t>9.88372093023248</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-29.89</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -2338,27 +2338,27 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-4878.8</t>
+          <t>-1585.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-3756.1</t>
+          <t>-1778.2</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1122</t>
+          <t>193</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-791.4882463678586</t>
+          <t>-654.1174894962272</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-937.52</t>
+          <t>101.42</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>393.0</t>
+          <t>528.0</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2505,17 +2505,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-11.9</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2535,82 +2535,82 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>437</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-3.80</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>23.27</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>24.0875</t>
+          <t>24.0025</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>22.983</t>
+          <t>23.041</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>-79.56</t>
+          <t>-113.04</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>24.99999999999994</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-52.78</t>
+          <t>-29.89</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -2630,27 +2630,27 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-4828.0</t>
+          <t>-4878.8</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-3160.1</t>
+          <t>-3756.1</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1667</t>
+          <t>-1122</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-764.9378570499535</t>
+          <t>-791.4882463678586</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-173.37</t>
+          <t>-937.52</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2782,12 +2782,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>393.0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2797,17 +2797,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-10.0</t>
+          <t>-13.25</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2827,92 +2827,92 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>78</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>437</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>23.27</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>24.14</t>
+          <t>24.0875</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>22.906</t>
+          <t>22.983</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>-74.95</t>
+          <t>-79.56</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.99999999999994</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.333333333333286</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-43.63</t>
+          <t>-52.78</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -2922,27 +2922,27 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-4584.8</t>
+          <t>-4828.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>-3192.1</t>
+          <t>-3160.1</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1392</t>
+          <t>-1667</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-872.4954031226443</t>
+          <t>-764.9378570499535</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1346.12</t>
+          <t>-173.37</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -2992,12 +2992,12 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>468.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-10.0</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -3139,57 +3139,57 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>437</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>23.68</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>24.2625</t>
+          <t>24.14</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>22.834</t>
+          <t>22.906</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>-61.97</t>
+          <t>-74.95</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-43.91</t>
+          <t>-43.63</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -3214,27 +3214,27 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-4983.6</t>
+          <t>-4584.8</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>-3463.0</t>
+          <t>-3192.1</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1520</t>
+          <t>-1392</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-786.3824557039895</t>
+          <t>-872.4954031226443</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1676.43</t>
+          <t>-1346.12</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>333.0</t>
+          <t>468.0</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3381,17 +3381,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>26.41</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-10.48</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -3431,57 +3431,57 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>437</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>23.88</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>24.2625</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>22.765</t>
+          <t>22.834</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>-48.85</t>
+          <t>-61.97</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>19.04761904761902</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>32.83</t>
+          <t>-43.91</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -3506,27 +3506,27 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-1971.4</t>
+          <t>-4983.6</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>-2934.8</t>
+          <t>-3463.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>-1520</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-624.5561555268883</t>
+          <t>-786.3824557039895</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1229.89</t>
+          <t>-1676.43</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -3576,12 +3576,12 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3673,17 +3673,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -3703,22 +3703,22 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -3728,67 +3728,67 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>24.58</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>24.8425</t>
+          <t>24.81</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>25.683</t>
+          <t>25.647</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>17.74</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>74.99999999999977</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>87.49999999999989</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>79.16666666666664</t>
-        </is>
-      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>117.07</t>
+          <t>185.41</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -3798,27 +3798,27 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>214.2</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>-311.7</t>
+          <t>-250.8</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>465</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>52.99625968923701</t>
+          <t>66.99855978745218</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>170.1</t>
+          <t>144.01</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3843,12 +3843,12 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>103.13</t>
+          <t>102.92</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3965,17 +3965,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>16.96</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -4000,17 +4000,17 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>35</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -4020,67 +4020,67 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>24.52</t>
+          <t>24.58</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>24.8875</t>
+          <t>24.8425</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>25.725</t>
+          <t>25.683</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>14.68</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.49999999999989</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>56.66666666666677</t>
+          <t>79.16666666666664</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>122.13</t>
+          <t>117.07</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -4090,27 +4090,27 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>-423.9</t>
+          <t>-311.7</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>364</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>31.70494339138414</t>
+          <t>52.99625968923701</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>258.4</t>
+          <t>170.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>103.13</t>
+          <t>102.92</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -4257,17 +4257,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>16.96</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -4287,22 +4287,22 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -4312,67 +4312,67 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.52</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>24.93</t>
+          <t>24.8875</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>25.767</t>
+          <t>25.725</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>23.33333333333344</t>
+          <t>56.66666666666677</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>-9.91</t>
+          <t>122.13</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -4382,27 +4382,27 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>-423.8</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>-385.6</t>
+          <t>-423.9</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-38</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-9.512021718183899</t>
+          <t>31.70494339138414</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>156.96</t>
+          <t>258.4</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>103.13</t>
+          <t>102.92</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
@@ -4519,12 +4519,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>-13.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -4604,67 +4604,67 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>24.985</t>
+          <t>24.93</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>25.813</t>
+          <t>25.767</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>20.00000000000028</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>6.666666666666771</t>
+          <t>23.33333333333344</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>63.37</t>
+          <t>-9.91</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
@@ -4674,27 +4674,27 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>-420.6</t>
+          <t>-423.8</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>-1148.2</t>
+          <t>-385.6</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>-38</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-39.77877162149947</t>
+          <t>-9.512021718183899</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>156.96</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>103.13</t>
+          <t>102.92</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4841,122 +4841,122 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>15.57</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>24.45</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>-13.0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>-2.02</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>-3.21</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>24.48</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>24.985</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>25.813</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>-2.04</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>-0.41</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>24.4</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>-0.41</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>-2.17</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>-3.15</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>24.5</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>25.0425</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>25.858</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>-4.87</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>-0.42</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.00000000000028</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.666666666666771</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>43.02</t>
+          <t>63.37</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
@@ -4966,27 +4966,27 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>-715.8</t>
+          <t>-420.6</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>-1256.3</t>
+          <t>-1148.2</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>727</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-61.44674194549375</t>
+          <t>-39.77877162149947</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-26.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>103.13</t>
+          <t>102.92</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -5133,17 +5133,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>15.57</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>43</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -5188,42 +5188,42 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>25.1025</t>
+          <t>25.0425</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>25.907</t>
+          <t>25.858</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2.083333333333371</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>45.58</t>
+          <t>43.02</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
@@ -5258,27 +5258,27 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>-676.6</t>
+          <t>-715.8</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>-1243.3</t>
+          <t>-1256.3</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>540</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-67.83488499889101</t>
+          <t>-61.44674194549375</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-9.78</t>
+          <t>-26.31</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -5303,12 +5303,12 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>103.13</t>
+          <t>102.92</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -5425,17 +5425,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>19.38</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>35</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -5480,42 +5480,42 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>25.16</t>
+          <t>25.1025</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>25.954</t>
+          <t>25.907</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-6.31</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>45.58</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
@@ -5550,27 +5550,27 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>-941.6</t>
+          <t>-676.6</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>-1198.4</t>
+          <t>-1243.3</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>566</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-78.39120433901441</t>
+          <t>-67.83488499889101</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-36.69</t>
+          <t>-9.78</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>103.13</t>
+          <t>102.92</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -5650,12 +5650,12 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -5717,17 +5717,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>19.38</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>41</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -5772,42 +5772,42 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>24.59</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>25.2175</t>
+          <t>25.16</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>25.999</t>
+          <t>25.954</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>-9.74</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>6.250000000000083</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>66.15</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
@@ -5842,27 +5842,27 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>-347.4</t>
+          <t>-941.6</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>-1026.4</t>
+          <t>-1198.4</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>256</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-85.97236219274511</t>
+          <t>-78.39120433901441</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>-36.69</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>103.13</t>
+          <t>102.92</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5994,69 +5994,69 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>7.61</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>14.53</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>24.55</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>0.81</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>2</t>
@@ -6064,22 +6064,22 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -6089,17 +6089,17 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>25.2675</t>
+          <t>25.2175</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26.047</t>
+          <t>25.999</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>-13.06</t>
+          <t>-9.74</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -6114,17 +6114,17 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.250000000000083</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.083333333333371</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>-58.68</t>
+          <t>66.15</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
@@ -6134,27 +6134,27 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>-1875.8</t>
+          <t>-347.4</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>-1182.1</t>
+          <t>-1026.4</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-693</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-102.8468898869734</t>
+          <t>-85.97236219274511</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-137.25</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>103.13</t>
+          <t>102.92</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -6301,12 +6301,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>12.80</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -6356,42 +6356,42 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>24.74</t>
+          <t>24.59</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>25.3225</t>
+          <t>25.2675</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26.091</t>
+          <t>26.047</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>-14.54</t>
+          <t>-13.06</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2.083333333333232</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>-95.01</t>
+          <t>-58.68</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
@@ -6426,27 +6426,27 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>-1796.8</t>
+          <t>-1875.8</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>-921.4</t>
+          <t>-1182.1</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-875</t>
+          <t>-693</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-96.59118567258551</t>
+          <t>-102.8468898869734</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-170.41</t>
+          <t>-137.25</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>103.13</t>
+          <t>102.92</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
@@ -6563,12 +6563,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -6593,17 +6593,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -6638,57 +6638,57 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>55</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>19.394</t>
+          <t>19.361</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>33.33333333333176</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>-532.96</t>
+          <t>-52.91</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
@@ -6718,27 +6718,27 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>-449.4</t>
+          <t>-485.8</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>-71.0</t>
+          <t>-317.7</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-378</t>
+          <t>-168</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-23.61623908160338</t>
+          <t>-18.98650937987177</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>69.94</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -6870,117 +6870,117 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-0.81</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>18.15</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>56.0</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>18.1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>55</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>18.14</t>
+          <t>18.13</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>19.436</t>
+          <t>19.394</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -6990,17 +6990,17 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33333333333176</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.1111111111106</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>-92.48</t>
+          <t>-532.96</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
@@ -7010,27 +7010,27 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>-818.6</t>
+          <t>-449.4</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>-425.3</t>
+          <t>-71.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-393</t>
+          <t>-378</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-40.6273421708739</t>
+          <t>-23.61623908160338</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-87.78</t>
+          <t>69.94</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
@@ -7110,12 +7110,12 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -7177,12 +7177,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -7222,52 +7222,52 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>55</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>18.17</t>
+          <t>18.14</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>18.79</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>19.492</t>
+          <t>19.436</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>-9.34</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>3.174603174603135</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>-92.48</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
@@ -7302,27 +7302,27 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>-487.2</t>
+          <t>-818.6</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>-565.3</t>
+          <t>-425.3</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>-393</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>-32.05454276520601</t>
+          <t>-40.6273421708739</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-62.57</t>
+          <t>-87.78</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -7454,29 +7454,29 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>61.0</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>-0.55</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>35.0</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>18.1</t>
@@ -7489,7 +7489,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -7514,77 +7514,77 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>-0.39</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>-3.30</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>-3.60</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>18.17</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>18.79</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>19.492</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>-9.34</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>-0.42</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>-0.49</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>-3.63</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>-3.42</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>18.19</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>18.875</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>19.544</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>-13.06</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>-0.47</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>5.73870573870565</t>
+          <t>3.174603174603135</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>24.73</t>
+          <t>13.82</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
@@ -7594,27 +7594,27 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>-390.4</t>
+          <t>-487.2</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>-518.7</t>
+          <t>-565.3</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>-26.5066568860711</t>
+          <t>-32.05454276520601</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>-14.25</t>
+          <t>-62.57</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -7746,137 +7746,137 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>-0.28</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>45.0</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>18.2</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>-3.63</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>-3.42</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>18.19</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>18.875</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>19.544</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>-13.06</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>-0.47</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>-3.98</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>-3.17</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>18.21</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>18.965</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>19.586</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>-16.63</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>-0.47</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>9.523809523809348</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>9.584859584859467</t>
+          <t>5.73870573870565</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>71.36</t>
+          <t>24.73</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
@@ -7886,27 +7886,27 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>-149.6</t>
+          <t>-390.4</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>-522.3</t>
+          <t>-518.7</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>-28.73552465984942</t>
+          <t>-26.5066568860711</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>-14.25</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -8038,12 +8038,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -8053,12 +8053,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -8103,47 +8103,47 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>55</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>18.21</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>18.965</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>19.624</t>
+          <t>19.586</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>-22.25</t>
+          <t>-16.63</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -8153,22 +8153,22 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>7.692307692307546</t>
+          <t>9.523809523809348</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>8.974358974358866</t>
+          <t>9.584859584859467</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>158.64</t>
+          <t>71.36</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
@@ -8178,27 +8178,27 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>307.4</t>
+          <t>-149.6</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>-524.2</t>
+          <t>-522.3</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>372</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>-34.8374925674095</t>
+          <t>-28.73552465984942</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>51.29</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -8330,12 +8330,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -8345,17 +8345,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -8390,52 +8390,52 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>55</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>19.135</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>19.624</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>-28.33</t>
+          <t>-22.25</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -8445,22 +8445,22 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11.53846153846145</t>
+          <t>7.692307692307546</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>8.791208791208685</t>
+          <t>8.974358974358866</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>93.96</t>
+          <t>158.64</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
@@ -8470,27 +8470,27 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>-32.0</t>
+          <t>307.4</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>-530.2</t>
+          <t>-524.2</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>831</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>-50.49762359874104</t>
+          <t>-34.8374925674095</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>87.24</t>
+          <t>51.29</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -8622,137 +8622,137 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>18.25</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>-1.11</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>34.0</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>0.81</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>18.2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>55</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>18.24</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>19.22</t>
+          <t>19.135</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.66</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>-36.05</t>
+          <t>-28.33</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>7.692307692307546</t>
+          <t>11.53846153846145</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>6.135531135530992</t>
+          <t>8.791208791208685</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>93.96</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
@@ -8762,27 +8762,27 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>-643.4</t>
+          <t>-32.0</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>-668.6</t>
+          <t>-530.2</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>498</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>-75.54027158916146</t>
+          <t>-50.49762359874104</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>7.54</t>
+          <t>87.24</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -8807,12 +8807,12 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -8979,72 +8979,72 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>55</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>18.43</t>
+          <t>18.24</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>19.3275</t>
+          <t>19.22</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>19.739</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>-42.82</t>
+          <t>-36.05</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>7.142857142856998</t>
+          <t>7.692307692307546</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>3.571428571428476</t>
+          <t>6.135531135530992</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>-20.66</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
@@ -9054,27 +9054,27 @@
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>-647.0</t>
+          <t>-643.4</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>-536.2</t>
+          <t>-668.6</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>-90.64594356094223</t>
+          <t>-75.54027158916146</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
@@ -9154,12 +9154,12 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -9221,29 +9221,29 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>18.2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>-0.83</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>18.15</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>0</t>
@@ -9271,72 +9271,72 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>55</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>18.43</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>19.4325</t>
+          <t>19.3275</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>19.777</t>
+          <t>19.739</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>-48.03</t>
+          <t>-42.82</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>3.571428571428372</t>
+          <t>7.142857142856998</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>1.190476190476143</t>
+          <t>3.571428571428476</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>-82.02</t>
+          <t>-20.66</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
@@ -9346,27 +9346,27 @@
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>-895.0</t>
+          <t>-647.0</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>-491.7</t>
+          <t>-536.2</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>-403</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>-112.4306885667275</t>
+          <t>-90.64594356094223</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-68.58</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
@@ -9533,94 +9533,94 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t>-0.87</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>-0.31</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>-1.91</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>-3.52</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>57.88</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>59.00999999999999</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>61.16</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>-3.51</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>-1.05</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>-0.31</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>-1.91</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>-3.52</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>57.88</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>59.00999999999999</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>61.16</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>-3.51</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>-1.08</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>-1.05</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AC32" t="inlineStr">
         <is>
           <t>3.030303030303074</t>
@@ -9713,7 +9713,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -9723,7 +9723,7 @@
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>11.63</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>11.63</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -10297,7 +10297,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -10307,7 +10307,7 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>11.63</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
@@ -10322,12 +10322,12 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
@@ -10409,7 +10409,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -10599,7 +10599,7 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>11.63</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>11.63</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -10906,12 +10906,12 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
@@ -10993,7 +10993,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -11183,7 +11183,7 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>11.63</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -11305,14 +11305,14 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="Q38" t="inlineStr">
         <is>
           <t>0</t>
@@ -11320,7 +11320,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>11.63</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -11490,12 +11490,12 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -11587,34 +11587,34 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="S39" t="inlineStr">
         <is>
           <t>0.61</t>
@@ -11757,7 +11757,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -11767,7 +11767,7 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>11.63</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -11782,12 +11782,12 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -11889,79 +11889,79 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>-1.29</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>-3.88</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>-1.35</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>58.76000000000001</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>61.13500000000001</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>61.974</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>-44.34</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>-1.12</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>-0.77</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>-1.29</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>-3.88</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>-1.35</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>58.76000000000001</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>61.13500000000001</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>61.974</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>-44.34</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>-1.12</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>-0.77</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AD40" t="inlineStr">
         <is>
           <t>21.22</t>
@@ -12049,7 +12049,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -12059,7 +12059,7 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>11.63</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -12074,12 +12074,12 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
@@ -12103,298 +12103,6 @@
         </is>
       </c>
       <c r="BF40" t="inlineStr">
-        <is>
-          <t>** 其他 - 農業科技業</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1240</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>-0.69</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>-1.76</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>-3.71</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>-1.03</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>59.14</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>61.42</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>62.06</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>-51.36</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>-1.04</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>-0.69</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>-18.38</t>
-        </is>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>-794.2</t>
-        </is>
-      </c>
-      <c r="AG41" t="inlineStr">
-        <is>
-          <t>-670.9</t>
-        </is>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>-123</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>-161.3903268328094</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>-230.65</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL41" t="inlineStr">
-        <is>
-          <t>茂生農經</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>農業科技業</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AP41" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="AQ41" t="inlineStr">
-        <is>
-          <t>7.656563769672629</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>-4.051061775258264</t>
-        </is>
-      </c>
-      <c r="AS41" t="inlineStr">
-        <is>
-          <t>-5.436727795897101</t>
-        </is>
-      </c>
-      <c r="AT41" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>5.89</t>
-        </is>
-      </c>
-      <c r="AV41" t="inlineStr">
-        <is>
-          <t>15.00</t>
-        </is>
-      </c>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>11.73</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>15.43%</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>6.21%</t>
-        </is>
-      </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>57.43</t>
-        </is>
-      </c>
-      <c r="BA41" t="inlineStr">
-        <is>
-          <t>2552</t>
-        </is>
-      </c>
-      <c r="BB41" t="inlineStr">
-        <is>
-          <t>禽畜飼料51.62%、蛋品30.92%、養殖12.44%、大宗原物料買賣4.82%、其他0.19% (2024年)</t>
-        </is>
-      </c>
-      <c r="BC41" t="inlineStr">
-        <is>
-          <t>茂生農經-農業科技業-上櫃</t>
-        </is>
-      </c>
-      <c r="BD41" t="inlineStr">
-        <is>
-          <t>農業科技業右上</t>
-        </is>
-      </c>
-      <c r="BE41" t="inlineStr">
-        <is>
-          <t>33.87</t>
-        </is>
-      </c>
-      <c r="BF41" t="inlineStr">
         <is>
           <t>** 其他 - 農業科技業</t>
         </is>

--- a/Result/checksun/農業科技業.xlsx
+++ b/Result/checksun/農業科技業.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>466.0</t>
+          <t>422.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -763,17 +763,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>33.47</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -783,142 +783,142 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>-1.72</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>-0.29</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-7.82</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>-3.18</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>20.76</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>22.52</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>23.26</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>-57.13</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>-0.78</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>14.89361702127652</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>9.23804328059642</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>-6.98</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>466</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>-2.26</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>-8.42</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>-2.30</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>20.82</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>22.735</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>23.27</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>-76.19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>-0.42</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>7.303807303807278</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>-12.31</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>6405.2</t>
+          <t>6503.8</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>7304.1</t>
+          <t>6991.5</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-898</t>
+          <t>-487</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-114.0754629947271</t>
+          <t>-113.9721704762695</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>-303.89</t>
+          <t>-113.4</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1050,44 +1050,44 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>-3.1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>466.0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-2.95</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20.35</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>9.12</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-0.47</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>-3.19</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1100,27 +1100,27 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>56</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>-22.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1135,52 +1135,52 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-7.79</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>20.82</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>22.735</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23.281</t>
+          <t>23.27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-92.85</t>
+          <t>-76.19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>12.82051282051282</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-15.01</t>
+          <t>-12.31</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1200,27 +1200,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>6176.2</t>
+          <t>6405.2</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>7266.7</t>
+          <t>7304.1</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1090</t>
+          <t>-898</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-79.56416095700345</t>
+          <t>-114.0754629947271</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>-641.44</t>
+          <t>-303.89</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1402,27 +1402,27 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>53</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>-20.0</t>
+          <t>-22.0</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1437,62 +1437,62 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-7.79</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>23.185</t>
+          <t>22.99</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>23.278</t>
+          <t>23.281</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-131.38</t>
+          <t>-92.85</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>9.090909090909092</t>
+          <t>12.82051282051282</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3.030303030303002</t>
+          <t>7.303807303807278</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-15.01</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1502,27 +1502,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>6998.4</t>
+          <t>6176.2</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>7315.0</t>
+          <t>7266.7</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-316</t>
+          <t>-1090</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>22.59500689859151</t>
+          <t>-79.56416095700345</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>-334.03</t>
+          <t>-641.44</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1639,12 +1639,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>437.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>34.66</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1704,27 +1704,27 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>75</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>-20.0</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1739,62 +1739,62 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-6.49</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>23.3875</t>
+          <t>23.185</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>23.276</t>
+          <t>23.278</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-201.99</t>
+          <t>-131.38</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.090909090909092</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.030303030303002</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1804,27 +1804,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>7548.0</t>
+          <t>6998.4</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>8143.3</t>
+          <t>7315.0</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-595</t>
+          <t>-316</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>87.43661315819058</t>
+          <t>22.59500689859151</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>94.23</t>
+          <t>-334.03</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>392.0</t>
+          <t>437.0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1971,17 +1971,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>31.09</t>
+          <t>34.66</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -2006,22 +2006,22 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>95</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -2041,47 +2041,47 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-6.49</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>23.6025</t>
+          <t>23.3875</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>23.26899999999999</t>
+          <t>23.276</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-362.37</t>
+          <t>-201.99</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -2091,12 +2091,12 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3.50877192982446</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-6.74</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2106,27 +2106,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>7479.2</t>
+          <t>7548.0</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>8019.4</t>
+          <t>8143.3</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-540</t>
+          <t>-595</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>86.20225112166432</t>
+          <t>87.43661315819058</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>94.23</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>380.0</t>
+          <t>392.0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2273,162 +2273,162 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>31.09</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>-3.19</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>-7</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>-6.0</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>-5.62</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>-5.73</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
           <t>22.25</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-9.34</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>23.6025</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>23.26899999999999</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>-362.37</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>-0.09</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>3.50877192982446</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>-6.74</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>466</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>-1.37</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>-5.20</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>22.56</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>23.7975</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>23.254</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>-3048.39</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>5.834353325173278</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>-1.83</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>8203.0</t>
+          <t>7479.2</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>8355.9</t>
+          <t>8019.4</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-152</t>
+          <t>-540</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>98.65805916179228</t>
+          <t>86.20225112166432</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>-22.09</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2453,12 +2453,12 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>286.0</t>
+          <t>380.0</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2575,17 +2575,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>22.68</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-11.3</t>
+          <t>-9.34</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -2625,82 +2625,82 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>-1.37</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>-5.20</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>22.56</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>23.7975</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>23.254</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>-3048.39</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>-0.26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>466</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>-0.70</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>-4.50</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>2.89</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>22.81</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>23.885</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>23.215</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>-461.19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>10.52631578947347</t>
-        </is>
-      </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>7.38474092207247</t>
+          <t>5.834353325173278</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -2710,27 +2710,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>8357.2</t>
+          <t>8203.0</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>8554.6</t>
+          <t>8355.9</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-197</t>
+          <t>-152</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>120.611723243151</t>
+          <t>98.65805916179228</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>-84.56</t>
+          <t>-22.09</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>236.0</t>
+          <t>286.0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2877,17 +2877,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>22.68</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-11.55</t>
+          <t>-11.3</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2947,62 +2947,62 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.81</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>23.9475</t>
+          <t>23.885</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>23.161</t>
+          <t>23.215</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-232.18</t>
+          <t>-461.19</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>6.97674418604645</t>
+          <t>10.52631578947347</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3.875968992247981</t>
+          <t>7.38474092207247</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -3012,27 +3012,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>7631.6</t>
+          <t>8357.2</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>8391.2</t>
+          <t>8554.6</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-759</t>
+          <t>-197</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>157.9154620547565</t>
+          <t>120.611723243151</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>32.79</t>
+          <t>-84.56</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3164,12 +3164,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>381.0</t>
+          <t>236.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3179,17 +3179,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>30.21</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-11.3</t>
+          <t>-11.55</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -3249,62 +3249,62 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>22.98</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.9475</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>23.101</t>
+          <t>23.161</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-156.43</t>
+          <t>-232.18</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4.651162790697579</t>
+          <t>6.97674418604645</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>9.88372093023248</t>
+          <t>3.875968992247981</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>-9.05</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -3314,27 +3314,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>8738.6</t>
+          <t>7631.6</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>8267.6</t>
+          <t>8391.2</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>-759</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>180.6660562163897</t>
+          <t>157.9154620547565</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>322.47</t>
+          <t>32.79</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>29.07</t>
+          <t>17.99</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>59</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -3551,37 +3551,37 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>24.665</t>
+          <t>24.61</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>25.498</t>
+          <t>25.446</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -3601,12 +3601,12 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>12.50000000000012</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>12.63</t>
+          <t>14.20</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -3616,27 +3616,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1010.4</t>
+          <t>1097.2</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>897.1</t>
+          <t>960.8</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>136</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-40.67090714022483</t>
+          <t>-30.95270620332881</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>12.16</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3783,17 +3783,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>29.07</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>55</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -3853,49 +3853,49 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>-3.27</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>24.53</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>24.665</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>25.498</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>9.63</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>-0.30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>-0.33</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>-3.24</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>24.64</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>24.7225</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>25.55</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>14.34</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>-0.29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
       <c r="AD12" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3903,12 +3903,12 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>37.50000000000005</t>
+          <t>12.50000000000012</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>12.63</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -3918,27 +3918,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>845.8</t>
+          <t>1010.4</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>831.6</t>
+          <t>897.1</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-50.27659455620269</t>
+          <t>-40.67090714022483</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>-85.65</t>
+          <t>12.16</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -4085,17 +4085,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -4130,17 +4130,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -4155,37 +4155,37 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>24.66</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>24.7675</t>
+          <t>24.7225</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>25.599</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>14.34</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -4195,22 +4195,22 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>37.50000000000033</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>66.66666666666667</t>
+          <t>37.50000000000005</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -4220,27 +4220,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>772.8</t>
+          <t>845.8</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>796.7</t>
+          <t>831.6</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-23</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-43.8453849716733</t>
+          <t>-50.27659455620269</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>-100.28</t>
+          <t>-85.65</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4372,12 +4372,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -4387,17 +4387,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -4427,12 +4427,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -4457,62 +4457,62 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>24.66</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>24.81</t>
+          <t>24.7675</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>25.647</t>
+          <t>25.599</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>17.74</t>
+          <t>17.32</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>74.99999999999977</t>
+          <t>37.50000000000033</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>87.49999999999989</t>
+          <t>66.66666666666667</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>-16.93</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -4522,27 +4522,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>663.4</t>
+          <t>772.8</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>798.6</t>
+          <t>796.7</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-135</t>
+          <t>-23</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-33.58449708943989</t>
+          <t>-43.8453849716733</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>-129.17</t>
+          <t>-100.28</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4689,17 +4689,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -4729,22 +4729,22 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -4759,62 +4759,62 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>24.58</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>24.8425</t>
+          <t>24.81</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>25.683</t>
+          <t>25.647</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>17.74</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
+          <t>74.99999999999977</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
           <t>87.49999999999989</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>79.16666666666664</t>
-        </is>
-      </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-16.93</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -4824,27 +4824,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>824.4</t>
+          <t>663.4</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>859.5</t>
+          <t>798.6</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-35</t>
+          <t>-135</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-16.20474274946435</t>
+          <t>-33.58449708943989</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>-90.09</t>
+          <t>-129.17</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4976,12 +4976,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4991,17 +4991,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>16.96</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -5036,17 +5036,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>35</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -5061,62 +5061,62 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>24.52</t>
+          <t>24.58</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>24.8875</t>
+          <t>24.8425</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>25.725</t>
+          <t>25.683</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>14.68</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.49999999999989</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>56.66666666666677</t>
+          <t>79.16666666666664</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>-19.34</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -5126,27 +5126,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>783.8</t>
+          <t>824.4</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>971.7</t>
+          <t>859.5</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-187</t>
+          <t>-35</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-2.771903468099598</t>
+          <t>-16.20474274946435</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>-88.14</t>
+          <t>-90.09</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>16.96</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -5333,22 +5333,22 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -5363,62 +5363,62 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.52</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>24.93</t>
+          <t>24.8875</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>25.767</t>
+          <t>25.725</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>23.33333333333344</t>
+          <t>56.66666666666677</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-19.34</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -5428,27 +5428,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>817.4</t>
+          <t>783.8</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>1010.0</t>
+          <t>971.7</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-192</t>
+          <t>-187</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>12.74874525864078</t>
+          <t>-2.771903468099598</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>-123.13</t>
+          <t>-88.14</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -5565,12 +5565,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -5665,62 +5665,62 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>24.985</t>
+          <t>24.93</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>25.813</t>
+          <t>25.767</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>20.00000000000028</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>6.666666666666771</t>
+          <t>23.33333333333344</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>-50.77</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -5730,27 +5730,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>820.6</t>
+          <t>817.4</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>1666.8</t>
+          <t>1010.0</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-846</t>
+          <t>-192</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>37.45411606078121</t>
+          <t>12.74874525864078</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>-95.76</t>
+          <t>-123.13</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -5897,162 +5897,162 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>15.57</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>24.45</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>-0.82</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>-2.02</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>-3.21</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>24.48</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>24.985</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>25.813</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>-2.04</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>-0.41</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>24.4</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>-0.62</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>20.00000000000028</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>6.666666666666771</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>-50.77</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>-2.17</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>-3.15</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>24.5</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>25.0425</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>25.858</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>-4.87</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>-0.42</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>-44.55</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>933.8</t>
+          <t>820.6</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1683.9</t>
+          <t>1666.8</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-750</t>
+          <t>-846</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>61.67528229035796</t>
+          <t>37.45411606078121</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>-45.32</t>
+          <t>-95.76</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -6184,177 +6184,177 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>-0.28</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0.29</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>17.5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>0.28</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>35.0</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>-2.28</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>17.55</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>-1.19</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>-2.91</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>-4.84</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>17.71</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>18.24</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>19.168</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>-5.80</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>-0.47</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>2.380952380952436</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>16.57</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>-1.63</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>-2.70</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>-4.56</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>17.84</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>18.335</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>19.212</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>-5.45</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>-0.47</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>-0.44</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>7.142857142857252</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>2.380952380952436</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>25.55</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1380.4</t>
+          <t>1355.6</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1099.5</t>
+          <t>1162.9</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>28.79025101718597</t>
+          <t>34.37109505330403</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>79.21</t>
+          <t>65.07</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -6571,42 +6571,42 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.84</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>18.4325</t>
+          <t>18.335</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19.263</t>
+          <t>19.212</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -6616,17 +6616,17 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.142857142857252</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.380952380952436</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>32.23</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -6636,27 +6636,27 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1458.0</t>
+          <t>1380.4</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1102.6</t>
+          <t>1099.5</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>280</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>19.6236819068325</t>
+          <t>28.79025101718597</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>156.47</t>
+          <t>79.21</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
@@ -6773,12 +6773,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -6788,12 +6788,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -6803,162 +6803,162 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
+          <t>17.5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>-2.51</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>-2.62</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-4.31</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
           <t>17.95</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>-2.28</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>18.4325</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>19.263</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>-4.06</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>32.23</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>-0.66</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>-2.50</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>-4.05</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>18.07</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>18.5325</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>19.315</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>-0.43</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>-0.43</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>11.1111111111106</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>25.36</t>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1092.4</t>
+          <t>1458.0</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>871.4</t>
+          <t>1102.6</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>355</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-5.257713884383525</t>
+          <t>19.6236819068325</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>156.47</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -7090,12 +7090,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -7105,17 +7105,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -7175,37 +7175,37 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.07</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>18.5325</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19.361</t>
+          <t>19.315</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>25.36</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -7240,27 +7240,27 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1006.6</t>
+          <t>1092.4</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>822.9</t>
+          <t>871.4</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>221</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-8.715777394892697</t>
+          <t>-5.257713884383525</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
@@ -7377,12 +7377,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -7407,17 +7407,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -7477,42 +7477,42 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19.394</t>
+          <t>19.361</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>33.33333333333176</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -7542,27 +7542,27 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>970.2</t>
+          <t>1006.6</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>871.0</t>
+          <t>822.9</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>183</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>-12.07432927856225</t>
+          <t>-8.715777394892697</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -7694,177 +7694,177 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-0.81</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>18.15</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>-3.42</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>56.0</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>18.1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>-3.13</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>-2.84</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>-3.78</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>18.13</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>18.66</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>19.394</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>-0.43</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>33.33333333333176</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>11.1111111111106</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>11.39</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>-3.10</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>-3.68</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>18.14</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>18.72</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>19.436</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>-5.71</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>-0.46</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>-0.43</t>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>-15.16</t>
-        </is>
-      </c>
-      <c r="AG25" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>818.6</t>
+          <t>970.2</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>964.9</t>
+          <t>871.0</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>-146</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>-16.22553113919524</t>
+          <t>-12.07432927856225</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>-21.3</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -8081,37 +8081,37 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>18.17</t>
+          <t>18.14</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>18.79</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19.492</t>
+          <t>19.436</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>-9.34</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>3.174603174603135</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>-32.37</t>
+          <t>-15.16</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -8146,27 +8146,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>747.2</t>
+          <t>818.6</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>1104.9</t>
+          <t>964.9</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-357</t>
+          <t>-146</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>-15.30216995260733</t>
+          <t>-16.22553113919524</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>-34.74</t>
+          <t>-21.3</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -8298,29 +8298,29 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>61.0</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
           <t>-0.55</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>35.0</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>18.1</t>
@@ -8383,47 +8383,47 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>18.19</t>
+          <t>18.17</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>18.875</t>
+          <t>18.79</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>19.544</t>
+          <t>19.492</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>-13.06</t>
+          <t>-9.34</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>5.73870573870565</t>
+          <t>3.174603174603135</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>-38.54</t>
+          <t>-32.37</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -8448,27 +8448,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>650.4</t>
+          <t>747.2</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>1058.3</t>
+          <t>1104.9</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-407</t>
+          <t>-357</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>-11.76840590645482</t>
+          <t>-15.30216995260733</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>-62.76</t>
+          <t>-34.74</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -8590,7 +8590,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -8600,177 +8600,177 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>-3.13</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>-3.63</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>-3.42</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>18.19</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>18.875</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>19.544</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>-13.06</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>-0.47</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>45.0</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>18.2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>-3.7</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>5.73870573870565</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>-38.54</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>-3.98</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>-3.17</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>18.21</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>18.965</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>19.586</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>-16.63</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>-0.47</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>9.523809523809348</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>9.584859584859467</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>-39.81</t>
-        </is>
-      </c>
-      <c r="AG28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>639.2</t>
+          <t>650.4</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>1061.9</t>
+          <t>1058.3</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-422</t>
+          <t>-407</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>-2.497228206233997</t>
+          <t>-11.76840590645482</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>-50.09</t>
+          <t>-62.76</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
@@ -8892,7 +8892,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -8902,12 +8902,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -8917,17 +8917,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -8937,142 +8937,142 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>-0.95</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>-1.98</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>-4.16</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>57.04000000000001</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>58.19</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>60.716</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>-2.99</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>-1.11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>-1.07</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>-15.64</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>-0.66</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>-1.88</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>-4.02</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>57.27999999999999</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>58.38</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>60.826</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>-1.60</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>-1.08</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>8.333333333333337</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>-55.96</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>378.6</t>
+          <t>453.2</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>859.7</t>
+          <t>537.2</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-481</t>
+          <t>-84</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>-150.9617885310265</t>
+          <t>-150.299019623976</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>-162.98</t>
+          <t>-146.65</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -9204,12 +9204,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -9219,17 +9219,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -9289,37 +9289,37 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>57.48</t>
+          <t>57.27999999999999</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>58.535</t>
+          <t>58.38</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>60.924</t>
+          <t>60.826</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -9329,7 +9329,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>-65.36</t>
+          <t>-55.96</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
@@ -9354,27 +9354,27 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>303.2</t>
+          <t>378.6</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>875.2</t>
+          <t>859.7</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-572</t>
+          <t>-481</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>-148.7771698727741</t>
+          <t>-150.9617885310265</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>-176.94</t>
+          <t>-162.98</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -9591,42 +9591,42 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>57.64</t>
+          <t>57.48</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>58.69000000000001</t>
+          <t>58.535</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>61.018</t>
+          <t>60.924</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>-54.30</t>
+          <t>-65.36</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
@@ -9656,27 +9656,27 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>377.4</t>
+          <t>303.2</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>825.8</t>
+          <t>875.2</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-448</t>
+          <t>-572</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>-143.6566541240782</t>
+          <t>-148.7771698727741</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>-209.64</t>
+          <t>-176.94</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -9808,177 +9808,177 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>57.6</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>57.2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>-0.53</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>-1.79</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>-3.82</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>57.64</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>58.69000000000001</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>61.018</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>-0.90</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>-1.07</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>-1.06</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>8.333333333333337</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>-54.30</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>-0.90</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>-1.90</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>-3.68</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>57.72000000000001</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>58.84</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>61.08600000000001</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>-1.10</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>-1.06</t>
-        </is>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>3.030303030303074</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>-52.09</t>
-        </is>
-      </c>
-      <c r="AG32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>382.2</t>
+          <t>377.4</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>797.8</t>
+          <t>825.8</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>-415</t>
+          <t>-448</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>-131.6598588426528</t>
+          <t>-143.6566541240782</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>-217.79</t>
+          <t>-209.64</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -10125,17 +10125,17 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -10175,74 +10175,74 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>-0.90</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>-1.90</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>-3.68</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>57.72000000000001</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>58.84</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>61.08600000000001</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>-1.10</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>-1.06</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>-0.31</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>-1.91</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>-3.52</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>57.88</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>59.00999999999999</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>61.16</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>-3.51</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>-1.08</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>-1.05</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AE33" t="inlineStr">
         <is>
           <t>3.030303030303074</t>
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>-26.96</t>
+          <t>-52.09</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
@@ -10260,27 +10260,27 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>621.2</t>
+          <t>382.2</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>850.5</t>
+          <t>797.8</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>-229</t>
+          <t>-415</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>-115.9992187108335</t>
+          <t>-131.6598588426528</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>-184.59</t>
+          <t>-217.79</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -10412,7 +10412,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -10432,12 +10432,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -10482,7 +10482,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -10497,62 +10497,62 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>57.88</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>59.15499999999999</t>
+          <t>59.00999999999999</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>61.244</t>
+          <t>61.16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>9.090909090909207</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>6.951871657754103</t>
+          <t>3.030303030303074</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>24.89</t>
+          <t>-26.96</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
@@ -10562,27 +10562,27 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>1340.8</t>
+          <t>621.2</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>1073.6</t>
+          <t>850.5</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>-229</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>-103.5276785793199</t>
+          <t>-115.9992187108335</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>-143.21</t>
+          <t>-184.59</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -10607,7 +10607,7 @@
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
@@ -10632,7 +10632,7 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
@@ -10704,7 +10704,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -10729,17 +10729,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -10774,24 +10774,24 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="T35" t="inlineStr">
         <is>
           <t>9</t>
@@ -10799,52 +10799,52 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>59.275</t>
+          <t>59.15499999999999</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>61.348</t>
+          <t>61.244</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>-9.35</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.090909090909207</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>24.89</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
@@ -10864,27 +10864,27 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>1447.2</t>
+          <t>1340.8</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>1129.3</t>
+          <t>1073.6</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>-96.31209410424667</t>
+          <t>-103.5276785793199</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>-75.02</t>
+          <t>-143.21</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
@@ -11006,7 +11006,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -11016,177 +11016,177 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>57.8</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>-1.58</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>0.20</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>58.0</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>-1.93</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>-2.02</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>-3.38</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>58.08</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>59.275</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>61.348</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>-9.35</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>-1.12</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>-1.02</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>6.951871657754103</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>28.15</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>-1.80</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>-3.40</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>59.37</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>61.458</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>-12.08</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>-1.12</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>-1.00</t>
-        </is>
-      </c>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>11.76470588235309</t>
-        </is>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>6.951871657754103</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="AG36" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>1274.2</t>
+          <t>1447.2</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>1177.4</t>
+          <t>1129.3</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>317</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>-100.1831906523396</t>
+          <t>-96.31209410424667</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>-74.14</t>
+          <t>-75.02</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -11318,12 +11318,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -11333,12 +11333,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -11408,12 +11408,12 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -11423,17 +11423,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>59.76000000000001</t>
+          <t>59.37</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>61.57</t>
+          <t>61.458</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>-16.13</t>
+          <t>-12.08</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -11443,22 +11443,22 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>9.090909090909207</t>
+          <t>11.76470588235309</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>16.36363636363636</t>
+          <t>6.951871657754103</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>-7.71</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
@@ -11468,27 +11468,27 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>1213.4</t>
+          <t>1274.2</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>1314.8</t>
+          <t>1177.4</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>-101</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>-104.9186051909249</t>
+          <t>-100.1831906523396</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-74.14</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">

--- a/Result/checksun/農業科技業.xlsx
+++ b/Result/checksun/農業科技業.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>422.0</t>
+          <t>117.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -763,17 +763,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>33.47</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -813,82 +813,82 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>117</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-7.82</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>22.3625</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>23.236</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-57.13</t>
+          <t>-44.48</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>14.89361702127652</t>
+          <t>8.695652173913023</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>9.23804328059642</t>
+          <t>7.863089731729819</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>-18.59</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -898,27 +898,27 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>6503.8</t>
+          <t>5181.6</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>6991.5</t>
+          <t>6364.8</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-487</t>
+          <t>-1183</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-113.9721704762695</t>
+          <t>-167.3465236768307</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>-113.4</t>
+          <t>-460.91</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -968,12 +968,12 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -998,12 +998,12 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>466.0</t>
+          <t>422.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>33.47</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1085,142 +1085,142 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>-0.73</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>-0.29</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>-7.82</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-3.18</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>20.76</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>22.52</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>23.26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>-57.13</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>-0.78</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>14.89361702127652</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>9.23804328059642</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>-6.98</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>466</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>-2.26</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>-8.42</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-2.30</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>20.82</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>22.735</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>23.27</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>-76.19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>-0.42</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>7.303807303807278</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>-12.31</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>6405.2</t>
+          <t>6503.8</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>7304.1</t>
+          <t>6991.5</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-898</t>
+          <t>-487</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-114.0754629947271</t>
+          <t>-113.9721704762695</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>-303.89</t>
+          <t>-113.4</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1352,177 +1352,177 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>-3.1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>466.0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-2.95</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20.35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>-2.26</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>-8.42</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-2.30</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>20.82</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>22.735</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>23.27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>-76.19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>-0.42</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>9.12</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-0.47</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-3.19</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>7.303807303807278</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>-12.31</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>-22.0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>466</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>-0.94</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>-7.79</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-1.25</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>21.2</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>22.99</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>23.281</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>-92.85</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.66</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>12.82051282051282</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>7.303807303807278</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>-15.01</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>6176.2</t>
+          <t>6405.2</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>7266.7</t>
+          <t>7304.1</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1090</t>
+          <t>-898</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-79.56416095700345</t>
+          <t>-114.0754629947271</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>-641.44</t>
+          <t>-303.89</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1709,92 +1709,92 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>53</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>-20.0</t>
+          <t>-22.0</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>117</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-7.79</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>23.185</t>
+          <t>22.99</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>23.278</t>
+          <t>23.281</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-131.38</t>
+          <t>-92.85</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>9.090909090909092</t>
+          <t>12.82051282051282</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3.030303030303002</t>
+          <t>7.303807303807278</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-15.01</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1804,27 +1804,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6998.4</t>
+          <t>6176.2</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>7315.0</t>
+          <t>7266.7</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-316</t>
+          <t>-1090</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>22.59500689859151</t>
+          <t>-79.56416095700345</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>-334.03</t>
+          <t>-641.44</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
@@ -1941,12 +1941,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>437.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1971,17 +1971,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>34.66</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -2011,92 +2011,92 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>75</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>-20.0</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>117</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-6.49</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>23.3875</t>
+          <t>23.185</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>23.276</t>
+          <t>23.278</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-201.99</t>
+          <t>-131.38</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.090909090909092</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.030303030303002</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2106,27 +2106,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>7548.0</t>
+          <t>6998.4</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>8143.3</t>
+          <t>7315.0</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-595</t>
+          <t>-316</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>87.43661315819058</t>
+          <t>22.59500689859151</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>94.23</t>
+          <t>-334.03</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2206,12 +2206,12 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>392.0</t>
+          <t>437.0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2273,17 +2273,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>31.09</t>
+          <t>34.66</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2313,17 +2313,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>95</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -2333,57 +2333,57 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>117</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-6.49</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>23.6025</t>
+          <t>23.3875</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>23.26899999999999</t>
+          <t>23.276</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-362.37</t>
+          <t>-201.99</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3.50877192982446</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-6.74</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -2408,27 +2408,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7479.2</t>
+          <t>7548.0</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>8019.4</t>
+          <t>8143.3</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-540</t>
+          <t>-595</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>86.20225112166432</t>
+          <t>87.43661315819058</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>94.23</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2453,12 +2453,12 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -2478,12 +2478,12 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>380.0</t>
+          <t>392.0</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2575,162 +2575,162 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>31.09</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-2.19</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>-7</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>-7.0</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>-5.62</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>-5.73</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
           <t>22.25</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>-9.34</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>23.6025</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>23.26899999999999</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>-362.37</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>-0.09</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>3.50877192982446</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>-6.74</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>466</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>-1.37</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>-5.20</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>22.56</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>23.7975</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>23.254</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>-3048.39</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>5.834353325173278</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>-1.83</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>8203.0</t>
+          <t>7479.2</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>8355.9</t>
+          <t>8019.4</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-152</t>
+          <t>-540</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>98.65805916179228</t>
+          <t>86.20225112166432</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>-22.09</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -2780,12 +2780,12 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>286.0</t>
+          <t>380.0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2877,17 +2877,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>22.68</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-11.3</t>
+          <t>-8.27</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2937,72 +2937,72 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>117</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-5.20</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>22.81</t>
+          <t>22.56</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>23.885</t>
+          <t>23.7975</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>23.215</t>
+          <t>23.254</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-461.19</t>
+          <t>-3048.39</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>10.52631578947347</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>7.38474092207247</t>
+          <t>5.834353325173278</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -3012,27 +3012,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>8357.2</t>
+          <t>8203.0</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>8554.6</t>
+          <t>8355.9</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-197</t>
+          <t>-152</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>120.611723243151</t>
+          <t>98.65805916179228</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>-84.56</t>
+          <t>-22.09</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3164,12 +3164,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>236.0</t>
+          <t>286.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3179,17 +3179,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>22.68</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-11.55</t>
+          <t>-10.22</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -3239,72 +3239,72 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>117</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.81</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>23.9475</t>
+          <t>23.885</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>23.161</t>
+          <t>23.215</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-232.18</t>
+          <t>-461.19</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>6.97674418604645</t>
+          <t>10.52631578947347</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3.875968992247981</t>
+          <t>7.38474092207247</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -3314,27 +3314,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>7631.6</t>
+          <t>8357.2</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>8391.2</t>
+          <t>8554.6</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-759</t>
+          <t>-197</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>157.9154620547565</t>
+          <t>120.611723243151</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>32.79</t>
+          <t>-84.56</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3466,44 +3466,44 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>33.0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>11.42</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>24.4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>17.99</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>24.25</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>0</t>
@@ -3521,42 +3521,42 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>58</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>33</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -3566,27 +3566,27 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.37</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>24.61</t>
+          <t>24.5625</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>25.446</t>
+          <t>25.398</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -3596,17 +3596,17 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27272727272697</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.090909090909001</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>14.20</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -3616,27 +3616,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1097.2</t>
+          <t>1199.2</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>960.8</t>
+          <t>931.3</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-30.95270620332881</t>
+          <t>-26.97600037401336</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>-5.1</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -3686,12 +3686,12 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>101.04</t>
+          <t>101.67</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3783,12 +3783,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>29.07</t>
+          <t>17.99</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3803,142 +3803,142 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>-0.74</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>-0.73</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>-3.29</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>24.43</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>24.61</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>25.446</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>6.99</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>-0.30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>-0.32</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>14.20</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>-3.27</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>24.53</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>24.665</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>25.498</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>9.63</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>-0.30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>-0.33</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>12.50000000000012</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>12.63</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1010.4</t>
+          <t>1097.2</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>897.1</t>
+          <t>960.8</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>136</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-40.67090714022483</t>
+          <t>-30.95270620332881</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>12.16</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>101.04</t>
+          <t>101.67</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
@@ -4018,12 +4018,12 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -4085,17 +4085,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>29.07</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>55</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -4140,64 +4140,64 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>33</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>-3.27</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>24.53</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>24.665</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>25.498</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>9.63</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>-0.30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
           <t>-0.33</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>-3.24</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>24.64</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>24.7225</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>25.55</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>14.34</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>-0.29</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
       <c r="AD13" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -4205,12 +4205,12 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>37.50000000000005</t>
+          <t>12.50000000000012</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>12.63</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -4220,27 +4220,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>845.8</t>
+          <t>1010.4</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>831.6</t>
+          <t>897.1</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-50.27659455620269</t>
+          <t>-40.67090714022483</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>-85.65</t>
+          <t>12.16</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -4265,12 +4265,12 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>101.04</t>
+          <t>101.67</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -4387,17 +4387,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -4432,62 +4432,62 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>33</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>24.66</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>24.7675</t>
+          <t>24.7225</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>25.599</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>14.34</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -4497,22 +4497,22 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>37.50000000000033</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>66.66666666666667</t>
+          <t>37.50000000000005</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -4522,27 +4522,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>772.8</t>
+          <t>845.8</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>796.7</t>
+          <t>831.6</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-23</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-43.8453849716733</t>
+          <t>-50.27659455620269</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>-100.28</t>
+          <t>-85.65</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>101.04</t>
+          <t>101.67</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4689,17 +4689,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -4749,72 +4749,72 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>33</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>24.66</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>24.81</t>
+          <t>24.7675</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>25.647</t>
+          <t>25.599</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>17.74</t>
+          <t>17.32</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>74.99999999999977</t>
+          <t>37.50000000000033</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>87.49999999999989</t>
+          <t>66.66666666666667</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>-16.93</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -4824,27 +4824,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>663.4</t>
+          <t>772.8</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>798.6</t>
+          <t>796.7</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-135</t>
+          <t>-23</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-33.58449708943989</t>
+          <t>-43.8453849716733</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>-129.17</t>
+          <t>-100.28</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>101.04</t>
+          <t>101.67</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4991,17 +4991,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -5031,92 +5031,92 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>33</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>24.58</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>24.8425</t>
+          <t>24.81</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>25.683</t>
+          <t>25.647</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>17.74</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
+          <t>74.99999999999977</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
           <t>87.49999999999989</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>79.16666666666664</t>
-        </is>
-      </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-16.93</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -5126,27 +5126,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>824.4</t>
+          <t>663.4</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>859.5</t>
+          <t>798.6</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-35</t>
+          <t>-135</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-16.20474274946435</t>
+          <t>-33.58449708943989</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>-90.09</t>
+          <t>-129.17</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>101.04</t>
+          <t>101.67</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
@@ -5226,12 +5226,12 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>16.96</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>35</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -5348,77 +5348,77 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>33</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>24.52</t>
+          <t>24.58</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>24.8875</t>
+          <t>24.8425</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>25.725</t>
+          <t>25.683</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>14.68</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.49999999999989</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>56.66666666666677</t>
+          <t>79.16666666666664</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>-19.34</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -5428,27 +5428,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>783.8</t>
+          <t>824.4</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>971.7</t>
+          <t>859.5</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-187</t>
+          <t>-35</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-2.771903468099598</t>
+          <t>-16.20474274946435</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>-88.14</t>
+          <t>-90.09</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>101.04</t>
+          <t>101.67</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -5595,17 +5595,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>16.96</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -5655,72 +5655,72 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>33</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.52</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>24.93</t>
+          <t>24.8875</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>25.767</t>
+          <t>25.725</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>23.33333333333344</t>
+          <t>56.66666666666677</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-19.34</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -5730,27 +5730,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>817.4</t>
+          <t>783.8</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>1010.0</t>
+          <t>971.7</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-192</t>
+          <t>-187</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>12.74874525864078</t>
+          <t>-2.771903468099598</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>-123.13</t>
+          <t>-88.14</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>101.04</t>
+          <t>101.67</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
@@ -5867,12 +5867,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -5957,72 +5957,72 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>33</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>24.985</t>
+          <t>24.93</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>25.813</t>
+          <t>25.767</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>20.00000000000028</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>6.666666666666771</t>
+          <t>23.33333333333344</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>-50.77</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -6032,27 +6032,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>820.6</t>
+          <t>817.4</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1666.8</t>
+          <t>1010.0</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-846</t>
+          <t>-192</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>37.45411606078121</t>
+          <t>12.74874525864078</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>-95.76</t>
+          <t>-123.13</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>101.04</t>
+          <t>101.67</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -6184,32 +6184,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>47.0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>-0.28</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>0.29</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -6239,22 +6239,22 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -6264,42 +6264,42 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>47</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>17.71</t>
+          <t>17.61</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>18.24</t>
+          <t>18.1475</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>19.168</t>
+          <t>19.127</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -6314,17 +6314,17 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.692307692307819</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2.380952380952436</t>
+          <t>4.945054945055042</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>16.57</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -6334,27 +6334,27 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1355.6</t>
+          <t>1320.8</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1162.9</t>
+          <t>1163.7</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>157</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>34.37109505330403</t>
+          <t>33.17794860050819</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>65.07</t>
+          <t>26.62</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -6486,177 +6486,177 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>-0.28</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0.29</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>17.5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>0.28</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>35.0</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>-2.28</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>17.55</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>-1.19</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>-2.91</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>-4.84</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>17.71</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>18.24</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>19.168</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>-5.80</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>-0.47</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>2.380952380952436</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>16.57</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>-1.63</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>-2.70</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>-4.56</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>17.84</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>18.335</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>19.212</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>-5.45</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>-0.47</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>-0.44</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>7.142857142857252</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>2.380952380952436</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>25.55</t>
-        </is>
-      </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1380.4</t>
+          <t>1355.6</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1099.5</t>
+          <t>1162.9</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>28.79025101718597</t>
+          <t>34.37109505330403</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>79.21</t>
+          <t>65.07</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -6788,12 +6788,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -6868,47 +6868,47 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>47</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.84</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>18.4325</t>
+          <t>18.335</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19.263</t>
+          <t>19.212</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -6918,17 +6918,17 @@
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.142857142857252</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.380952380952436</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>32.23</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -6938,27 +6938,27 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1458.0</t>
+          <t>1380.4</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1102.6</t>
+          <t>1099.5</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>280</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>19.6236819068325</t>
+          <t>28.79025101718597</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>156.47</t>
+          <t>79.21</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
@@ -7075,12 +7075,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -7090,12 +7090,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -7105,162 +7105,162 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
+          <t>17.5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>-2.51</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>-2.62</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-4.31</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
           <t>17.95</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>-2.28</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>18.4325</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>19.263</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-4.06</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>32.23</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>-0.66</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>-2.50</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>-4.05</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>18.07</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>18.5325</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>19.315</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>-0.43</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>-0.43</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>11.1111111111106</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>25.36</t>
-        </is>
-      </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1092.4</t>
+          <t>1458.0</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>871.4</t>
+          <t>1102.6</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>355</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-5.257713884383525</t>
+          <t>19.6236819068325</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>156.47</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -7407,17 +7407,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -7472,42 +7472,42 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>47</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.07</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>18.5325</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19.361</t>
+          <t>19.315</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>25.36</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -7542,27 +7542,27 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>1006.6</t>
+          <t>1092.4</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>822.9</t>
+          <t>871.4</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>221</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>-8.715777394892697</t>
+          <t>-5.257713884383525</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
@@ -7679,12 +7679,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -7709,17 +7709,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -7774,47 +7774,47 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>47</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19.394</t>
+          <t>19.361</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>33.33333333333176</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
@@ -7834,7 +7834,7 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -7844,27 +7844,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>970.2</t>
+          <t>1006.6</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>871.0</t>
+          <t>822.9</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>183</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>-12.07432927856225</t>
+          <t>-8.715777394892697</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -7996,177 +7996,177 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-0.81</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>18.15</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>-3.42</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>56.0</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>18.1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>-3.13</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>-2.84</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>-3.78</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>18.13</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>18.66</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>19.394</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>-0.43</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>33.33333333333176</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>11.1111111111106</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>11.39</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>-3.10</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>-3.68</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>18.14</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>18.72</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>19.436</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>-5.71</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>-0.46</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>-0.43</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>-15.16</t>
-        </is>
-      </c>
-      <c r="AG26" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>818.6</t>
+          <t>970.2</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>964.9</t>
+          <t>871.0</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-146</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>-16.22553113919524</t>
+          <t>-12.07432927856225</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>-21.3</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -8378,42 +8378,42 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>47</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>18.17</t>
+          <t>18.14</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>18.79</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>19.492</t>
+          <t>19.436</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>-9.34</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -8423,7 +8423,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>3.174603174603135</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>-32.37</t>
+          <t>-15.16</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -8448,27 +8448,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>747.2</t>
+          <t>818.6</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>1104.9</t>
+          <t>964.9</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-357</t>
+          <t>-146</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>-15.30216995260733</t>
+          <t>-16.22553113919524</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>-34.74</t>
+          <t>-21.3</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
@@ -8590,7 +8590,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -8600,29 +8600,29 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>61.0</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>-0.55</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>35.0</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>18.1</t>
@@ -8680,52 +8680,52 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>47</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>18.19</t>
+          <t>18.17</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>18.875</t>
+          <t>18.79</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>19.544</t>
+          <t>19.492</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>-13.06</t>
+          <t>-9.34</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>5.73870573870565</t>
+          <t>3.174603174603135</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>-38.54</t>
+          <t>-32.37</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -8750,27 +8750,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>650.4</t>
+          <t>747.2</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>1058.3</t>
+          <t>1104.9</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-407</t>
+          <t>-357</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>-11.76840590645482</t>
+          <t>-15.30216995260733</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>-62.76</t>
+          <t>-34.74</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
@@ -8887,12 +8887,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -8902,12 +8902,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -8917,162 +8917,162 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>-1.79</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>-4.25</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>58.04</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>60.614</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>-1.07</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>-1.07</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>35.71428571428575</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>11.90476190476192</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>16.97</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>-0.95</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>-1.98</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>-4.16</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>57.04000000000001</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>58.19</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>60.716</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>-2.99</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>-1.11</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>-15.64</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>453.2</t>
+          <t>538.4</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>537.2</t>
+          <t>460.3</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-84</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>-150.299019623976</t>
+          <t>-148.1662574522824</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>-146.65</t>
+          <t>-136.44</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
@@ -9152,12 +9152,12 @@
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -9204,12 +9204,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -9219,17 +9219,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -9239,142 +9239,142 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t>0.88</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>-0.95</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>-1.98</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>-4.16</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>57.04000000000001</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>58.19</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>60.716</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>-2.99</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>-1.11</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>-1.07</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>-15.64</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>-0.66</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>-1.88</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>-4.02</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>57.27999999999999</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>58.38</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>60.826</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>-1.60</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>-1.08</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>8.333333333333337</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>-55.96</t>
-        </is>
-      </c>
-      <c r="AG30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>378.6</t>
+          <t>453.2</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>859.7</t>
+          <t>537.2</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-481</t>
+          <t>-84</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>-150.9617885310265</t>
+          <t>-150.299019623976</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>-162.98</t>
+          <t>-146.65</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
@@ -9454,12 +9454,12 @@
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -9521,17 +9521,17 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -9591,37 +9591,37 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>57.48</t>
+          <t>57.27999999999999</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>58.535</t>
+          <t>58.38</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>60.924</t>
+          <t>60.826</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>-65.36</t>
+          <t>-55.96</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
@@ -9656,27 +9656,27 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>303.2</t>
+          <t>378.6</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>875.2</t>
+          <t>859.7</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-572</t>
+          <t>-481</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>-148.7771698727741</t>
+          <t>-150.9617885310265</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>-176.94</t>
+          <t>-162.98</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -9863,7 +9863,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -9893,42 +9893,42 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>57.64</t>
+          <t>57.48</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>58.69000000000001</t>
+          <t>58.535</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>61.018</t>
+          <t>60.924</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>-54.30</t>
+          <t>-65.36</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
@@ -9958,27 +9958,27 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>377.4</t>
+          <t>303.2</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>825.8</t>
+          <t>875.2</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>-448</t>
+          <t>-572</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>-143.6566541240782</t>
+          <t>-148.7771698727741</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>-209.64</t>
+          <t>-176.94</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
@@ -10058,12 +10058,12 @@
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -10110,177 +10110,177 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>57.6</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>-1.05</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>57.2</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>-0.53</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>-1.79</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>-3.82</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>57.64</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>58.69000000000001</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>61.018</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>-0.90</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>-1.07</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>-1.06</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>8.333333333333337</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>-54.30</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>-0.90</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>-1.90</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>-3.68</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>57.72000000000001</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>58.84</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>61.08600000000001</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>-1.10</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>-1.06</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>3.030303030303074</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>-52.09</t>
-        </is>
-      </c>
-      <c r="AG33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>382.2</t>
+          <t>377.4</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>797.8</t>
+          <t>825.8</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>-415</t>
+          <t>-448</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>-131.6598588426528</t>
+          <t>-143.6566541240782</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>-217.79</t>
+          <t>-209.64</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
@@ -10330,12 +10330,12 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
@@ -10345,7 +10345,7 @@
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -10412,44 +10412,44 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>-0.87</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>57.2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t>-0.35</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>57.7</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>-1.41</t>
-        </is>
-      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>0</t>
@@ -10467,7 +10467,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -10477,74 +10477,74 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>-0.90</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>-1.90</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>-3.68</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>57.72000000000001</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>58.84</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>61.08600000000001</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>-1.10</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>-1.06</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>-0.31</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>-1.91</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>-3.52</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>57.88</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>59.00999999999999</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>61.16</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>-3.51</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>-1.08</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>-1.05</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AE34" t="inlineStr">
         <is>
           <t>3.030303030303074</t>
@@ -10552,7 +10552,7 @@
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>-26.96</t>
+          <t>-52.09</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
@@ -10562,27 +10562,27 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>621.2</t>
+          <t>382.2</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>850.5</t>
+          <t>797.8</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>-229</t>
+          <t>-415</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>-115.9992187108335</t>
+          <t>-131.6598588426528</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>-184.59</t>
+          <t>-217.79</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -10607,7 +10607,7 @@
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
@@ -10662,12 +10662,12 @@
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
@@ -10704,7 +10704,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -10714,7 +10714,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -10799,62 +10799,62 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>57.88</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>59.15499999999999</t>
+          <t>59.00999999999999</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>61.244</t>
+          <t>61.16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>9.090909090909207</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>6.951871657754103</t>
+          <t>3.030303030303074</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>24.89</t>
+          <t>-26.96</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
@@ -10864,27 +10864,27 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>1340.8</t>
+          <t>621.2</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>1073.6</t>
+          <t>850.5</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>-229</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>-103.5276785793199</t>
+          <t>-115.9992187108335</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>-143.21</t>
+          <t>-184.59</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
@@ -10934,12 +10934,12 @@
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
@@ -11006,7 +11006,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -11031,17 +11031,17 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -11101,52 +11101,52 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>59.275</t>
+          <t>59.15499999999999</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>61.348</t>
+          <t>61.244</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>-9.35</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.090909090909207</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>24.89</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
@@ -11166,27 +11166,27 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>1447.2</t>
+          <t>1340.8</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>1129.3</t>
+          <t>1073.6</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>-96.31209410424667</t>
+          <t>-103.5276785793199</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>-75.02</t>
+          <t>-143.21</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -11318,177 +11318,177 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>57.8</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>-1.4</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>-2.02</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>-3.38</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>58.08</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>59.275</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>61.348</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>-9.35</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>-1.12</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>-1.02</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>0.20</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>58.0</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>-1.93</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>6.951871657754103</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>28.15</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>-1.80</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>-3.40</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>59.37</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>61.458</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>-12.08</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>-1.12</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>-1.00</t>
-        </is>
-      </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>11.76470588235309</t>
-        </is>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>6.951871657754103</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="AG37" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>1274.2</t>
+          <t>1447.2</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>1177.4</t>
+          <t>1129.3</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>317</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>-100.1831906523396</t>
+          <t>-96.31209410424667</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>-74.14</t>
+          <t>-75.02</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
@@ -11543,7 +11543,7 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="BD37" t="inlineStr">

--- a/Result/checksun/農業科技業.xlsx
+++ b/Result/checksun/農業科技業.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH37"/>
+  <dimension ref="A1:BH33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -738,7 +738,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>179.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -763,162 +763,162 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>14.20</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>20.15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>-23.0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>-1.95</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-7.29</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>-4.46</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
           <t>20.55</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>22.165</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>23.199</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>-37.90</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>-0.85</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>-0.62</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>7.863089731729819</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>-13.16</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>-0.82</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>-7.34</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>-3.76</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>20.72</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>22.3625</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>23.236</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>-44.48</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>-0.80</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>-0.56</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>8.695652173913023</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>7.863089731729819</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>-18.59</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>5181.6</t>
+          <t>5370.6</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>6364.8</t>
+          <t>6184.5</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1183</t>
+          <t>-813</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-167.3465236768307</t>
+          <t>-234.7407220160158</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>-460.91</t>
+          <t>-605.41</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -968,12 +968,12 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>422.0</t>
+          <t>117.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>33.47</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1115,82 +1115,82 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>179</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-7.82</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>22.3625</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>23.236</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-57.13</t>
+          <t>-44.48</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>14.89361702127652</t>
+          <t>8.695652173913023</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>9.23804328059642</t>
+          <t>7.863089731729819</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>-18.59</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1200,27 +1200,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>6503.8</t>
+          <t>5181.6</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>6991.5</t>
+          <t>6364.8</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-487</t>
+          <t>-1183</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-113.9721704762695</t>
+          <t>-167.3465236768307</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>-113.4</t>
+          <t>-460.91</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>466.0</t>
+          <t>422.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1367,17 +1367,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>33.47</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1412,87 +1412,87 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>79</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>179</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-7.82</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>20.76</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>22.735</t>
+          <t>22.52</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>23.27</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-76.19</t>
+          <t>-57.13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.89361702127652</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>7.303807303807278</t>
+          <t>9.23804328059642</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-12.31</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1502,27 +1502,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>6405.2</t>
+          <t>6503.8</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>7304.1</t>
+          <t>6991.5</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-898</t>
+          <t>-487</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-114.0754629947271</t>
+          <t>-113.9721704762695</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>-303.89</t>
+          <t>-113.4</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1654,177 +1654,177 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>-3.1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>466.0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-2.95</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20.35</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-0.99</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>-2.26</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>-8.42</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-2.30</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>20.82</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>22.735</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>23.27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>-76.19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>-0.42</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>9.12</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-0.47</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-2.19</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>7.303807303807278</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>-12.31</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>-22.0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>-0.94</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>-7.79</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>-1.25</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>21.2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>22.99</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>23.281</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>-92.85</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>-0.66</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>12.82051282051282</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>7.303807303807278</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>-15.01</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6176.2</t>
+          <t>6405.2</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>7266.7</t>
+          <t>7304.1</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1090</t>
+          <t>-898</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-79.56416095700345</t>
+          <t>-114.0754629947271</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>-641.44</t>
+          <t>-303.89</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1971,12 +1971,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -2006,97 +2006,97 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>53</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>-20.0</t>
+          <t>-22.0</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>179</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-7.79</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>23.185</t>
+          <t>22.99</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>23.278</t>
+          <t>23.281</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-131.38</t>
+          <t>-92.85</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>9.090909090909092</t>
+          <t>12.82051282051282</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3.030303030303002</t>
+          <t>7.303807303807278</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-15.01</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2106,27 +2106,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6998.4</t>
+          <t>6176.2</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>7315.0</t>
+          <t>7266.7</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-316</t>
+          <t>-1090</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>22.59500689859151</t>
+          <t>-79.56416095700345</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>-334.03</t>
+          <t>-641.44</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
@@ -2243,12 +2243,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>437.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2273,17 +2273,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>34.66</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2308,97 +2308,97 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>75</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-5.0</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>179</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-6.49</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>23.3875</t>
+          <t>23.185</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>23.276</t>
+          <t>23.278</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-201.99</t>
+          <t>-131.38</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.090909090909092</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.030303030303002</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -2408,27 +2408,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7548.0</t>
+          <t>6998.4</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>8143.3</t>
+          <t>7315.0</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-595</t>
+          <t>-316</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>87.43661315819058</t>
+          <t>22.59500689859151</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>94.23</t>
+          <t>-334.03</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2453,12 +2453,12 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -2478,12 +2478,12 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>392.0</t>
+          <t>437.0</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2575,17 +2575,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>31.09</t>
+          <t>34.66</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2610,82 +2610,82 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-7.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>179</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-6.49</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>23.6025</t>
+          <t>23.3875</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>23.26899999999999</t>
+          <t>23.276</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-362.37</t>
+          <t>-201.99</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3.50877192982446</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-6.74</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -2710,27 +2710,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>7479.2</t>
+          <t>7548.0</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>8019.4</t>
+          <t>8143.3</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-540</t>
+          <t>-595</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>86.20225112166432</t>
+          <t>87.43661315819058</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>94.23</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -2780,12 +2780,12 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>380.0</t>
+          <t>392.0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2877,162 +2877,162 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>31.09</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-4.22</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>-5.62</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>-5.73</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
           <t>22.25</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>-8.27</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>23.6025</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>23.26899999999999</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>-362.37</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>-0.09</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>3.50877192982446</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>-6.74</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>-1.37</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>-5.20</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>22.56</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>23.7975</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>23.254</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>-3048.39</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>5.834353325173278</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>-1.83</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>8203.0</t>
+          <t>7479.2</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>8355.9</t>
+          <t>8019.4</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-152</t>
+          <t>-540</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>98.65805916179228</t>
+          <t>86.20225112166432</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>-22.09</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
@@ -3149,27 +3149,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>6578</t>
+          <t>6508</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>286.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3179,17 +3179,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>22.68</t>
+          <t>13.15</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-10.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -3224,87 +3224,87 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16.0</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>38</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>22.81</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>23.885</t>
+          <t>24.5175</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>23.215</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-461.19</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>10.52631578947347</t>
+          <t>27.27272727272697</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>7.38474092207247</t>
+          <t>18.18181818181799</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>20.90</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -3314,27 +3314,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>8357.2</t>
+          <t>1181.2</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>8554.6</t>
+          <t>977.0</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-197</t>
+          <t>204</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>120.611723243151</t>
+          <t>-25.32931992241485</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>-84.56</t>
+          <t>-16.27</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>達邦蛋白</t>
+          <t>惠光</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -3359,57 +3359,57 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>-31.27243717590746</t>
+          <t>2.573577462780557</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-20.91614265387616</t>
+          <t>-50.30308961435948</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>-16.94616644850042</t>
+          <t>-1.393799426610701</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>101.67</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>21.13%</t>
+          <t>19.95%</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>4.80%</t>
+          <t>10.66%</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -3419,32 +3419,32 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>水解黃豆(月生)(月太)蛋白100.00% (2024年)</t>
+          <t>農業科學73.60%、環境科技26.40% (2024年)</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>達邦蛋白-農業科技業-上櫃</t>
+          <t>惠光-農業科技業-上櫃</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>農業科技業平</t>
+          <t>農業科技業右下</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>14.33</t>
+          <t>26.85</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>** 食品 - 原物料</t>
+          <t>** 石化及塑橡膠 - 塑膠製品、農藥** 其他 - 農業科技業</t>
         </is>
       </c>
     </row>
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>38</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -3843,12 +3843,12 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>38</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>38</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>38</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -4744,17 +4744,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>38</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -5036,27 +5036,27 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>38</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -5333,32 +5333,32 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>38</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -5565,27 +5565,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>4171</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -5595,17 +5595,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>16.96</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -5630,97 +5630,97 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>-1.26</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>-3.16</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>-5.46</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>17.47</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>18.04</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>19.082</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>-6.09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>-1.48</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>-3.26</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>24.52</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>24.8875</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>25.725</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>9.55</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>-0.36</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>-0.39</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>56.66666666666677</t>
+          <t>2.564102564102625</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>-19.34</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -5730,27 +5730,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>783.8</t>
+          <t>1205.0</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>971.7</t>
+          <t>1148.7</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-187</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-2.771903468099598</t>
+          <t>24.01367745167646</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>-88.14</t>
+          <t>-26.39</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>惠光</t>
+          <t>瑞基</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
@@ -5785,47 +5785,47 @@
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>2.573577462780557</t>
+          <t>-2.15502457985595</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-50.30308961435948</t>
+          <t>-43.05343003526515</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>-1.393799426610701</t>
+          <t>3.446587753909104</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>101.67</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>19.95%</t>
+          <t>73.45%</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>10.66%</t>
+          <t>-47.53%</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
@@ -5835,17 +5835,17 @@
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>農業科學73.60%、環境科技26.40% (2024年)</t>
+          <t>檢驗試劑87.44%、檢測設備9.39%、其他產品3.17% (2024年)</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>惠光-農業科技業-上櫃</t>
+          <t>瑞基-農業科技業-上櫃</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
@@ -5855,39 +5855,39 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>26.85</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>** 石化及塑橡膠 - 塑膠製品、農藥** 其他 - 農業科技業</t>
+          <t>** 其他 - 農業科技業** 醫療器材 - 生物檢測</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>4171</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -5897,17 +5897,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -5942,87 +5942,87 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>28</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>17.61</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>24.93</t>
+          <t>18.1475</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>25.767</t>
+          <t>19.127</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>7.692307692307819</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>23.33333333333344</t>
+          <t>4.945054945055042</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -6032,27 +6032,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>817.4</t>
+          <t>1320.8</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1010.0</t>
+          <t>1163.7</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-192</t>
+          <t>157</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>12.74874525864078</t>
+          <t>33.17794860050819</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>-123.13</t>
+          <t>26.62</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>惠光</t>
+          <t>瑞基</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
@@ -6087,47 +6087,47 @@
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>2.573577462780557</t>
+          <t>-2.15502457985595</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-50.30308961435948</t>
+          <t>-43.05343003526515</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>-1.393799426610701</t>
+          <t>3.446587753909104</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>101.67</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>19.95%</t>
+          <t>73.45%</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>10.66%</t>
+          <t>-47.53%</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
@@ -6137,17 +6137,17 @@
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>農業科學73.60%、環境科技26.40% (2024年)</t>
+          <t>檢驗試劑87.44%、檢測設備9.39%、其他產品3.17% (2024年)</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>惠光-農業科技業-上櫃</t>
+          <t>瑞基-農業科技業-上櫃</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -6157,12 +6157,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>26.85</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>** 石化及塑橡膠 - 塑膠製品、農藥** 其他 - 農業科技業</t>
+          <t>** 其他 - 農業科技業** 醫療器材 - 生物檢測</t>
         </is>
       </c>
     </row>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -6199,17 +6199,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -6219,142 +6219,142 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t>-1.45</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>-1.19</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>-2.91</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>-4.84</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>17.71</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>18.24</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>19.168</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>-5.80</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>-0.47</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>2.380952380952436</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>16.57</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>-2.96</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>-5.12</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>17.61</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>18.1475</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>19.127</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>-4.10</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>-0.47</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>7.692307692307819</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>4.945054945055042</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>13.50</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1320.8</t>
+          <t>1355.6</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1163.7</t>
+          <t>1162.9</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>33.17794860050819</t>
+          <t>34.37109505330403</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>26.62</t>
+          <t>65.07</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -6501,17 +6501,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -6551,57 +6551,57 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>28</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>17.71</t>
+          <t>17.84</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>18.24</t>
+          <t>18.335</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19.168</t>
+          <t>19.212</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.142857142857252</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>16.57</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -6636,27 +6636,27 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1355.6</t>
+          <t>1380.4</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1162.9</t>
+          <t>1099.5</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>280</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>34.37109505330403</t>
+          <t>28.79025101718597</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>65.07</t>
+          <t>79.21</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -6788,12 +6788,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -6823,142 +6823,142 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t>-1.45</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>-2.51</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>-2.62</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-4.31</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>17.95</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>18.4325</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>19.263</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>-4.06</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>32.23</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>-1.63</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>-2.70</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>-4.56</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>17.84</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>18.335</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>19.212</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>-5.45</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>-0.47</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>-0.44</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>7.142857142857252</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>2.380952380952436</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>25.55</t>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1380.4</t>
+          <t>1458.0</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1099.5</t>
+          <t>1102.6</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>355</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>28.79025101718597</t>
+          <t>19.6236819068325</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>79.21</t>
+          <t>156.47</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
@@ -7075,12 +7075,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -7090,12 +7090,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -7105,17 +7105,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -7145,77 +7145,77 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>28</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.07</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>18.4325</t>
+          <t>18.5325</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19.263</t>
+          <t>19.315</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -7225,12 +7225,12 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.1111111111106</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>32.23</t>
+          <t>25.36</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -7240,27 +7240,27 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1458.0</t>
+          <t>1092.4</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1102.6</t>
+          <t>871.4</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>221</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>19.6236819068325</t>
+          <t>-5.257713884383525</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>156.47</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -7407,17 +7407,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -7467,47 +7467,47 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>28</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>18.07</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>18.5325</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19.315</t>
+          <t>19.361</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>25.36</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -7542,27 +7542,27 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>1092.4</t>
+          <t>1006.6</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>871.4</t>
+          <t>822.9</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>183</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>-5.257713884383525</t>
+          <t>-8.715777394892697</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
@@ -7679,12 +7679,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -7709,17 +7709,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -7754,77 +7754,77 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>28</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.13</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19.361</t>
+          <t>19.394</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
           <t>-0.43</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>-0.43</t>
-        </is>
-      </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33333333333176</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
@@ -7834,7 +7834,7 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -7844,27 +7844,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>1006.6</t>
+          <t>970.2</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>822.9</t>
+          <t>871.0</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>-8.715777394892697</t>
+          <t>-12.07432927856225</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
@@ -7981,27 +7981,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -8011,17 +8011,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -8066,77 +8066,77 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>56.88</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>57.895</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19.394</t>
+          <t>60.504</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>33.33333333333176</t>
+          <t>35.71428571428575</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>11.1111111111106</t>
+          <t>23.80952380952384</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -8146,27 +8146,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>970.2</t>
+          <t>469.4</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>871.0</t>
+          <t>423.4</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>-12.07432927856225</t>
+          <t>-149.6403341951938</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>-157.75</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>瑞基</t>
+          <t>茂生農經</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -8191,57 +8191,57 @@
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>-2.15502457985595</t>
+          <t>7.656563769672629</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>-43.05343003526515</t>
+          <t>-4.051061775258264</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>3.446587753909104</t>
+          <t>-5.436727795897101</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>73.45%</t>
+          <t>15.43%</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>-47.53%</t>
+          <t>6.21%</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
@@ -8251,91 +8251,91 @@
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>檢驗試劑87.44%、檢測設備9.39%、其他產品3.17% (2024年)</t>
+          <t>禽畜飼料51.62%、蛋品30.92%、養殖12.44%、大宗原物料買賣4.82%、其他0.19% (2024年)</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
-          <t>瑞基-農業科技業-上櫃</t>
+          <t>茂生農經-農業科技業-上櫃</t>
         </is>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>農業科技業右下</t>
+          <t>農業科技業右上</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>33.87</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>** 其他 - 農業科技業** 醫療器材 - 生物檢測</t>
+          <t>** 其他 - 農業科技業</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>0.88</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>56.0</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>18.1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>-3.13</t>
-        </is>
-      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>0</t>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -8363,82 +8363,82 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>18.14</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>58.04</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>19.436</t>
+          <t>60.614</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.71428571428575</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.90476190476192</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>-15.16</t>
+          <t>16.97</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -8448,27 +8448,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>818.6</t>
+          <t>538.4</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>964.9</t>
+          <t>460.3</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-146</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>-16.22553113919524</t>
+          <t>-148.1662574522824</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>-21.3</t>
+          <t>-136.44</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>瑞基</t>
+          <t>茂生農經</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
@@ -8503,47 +8503,47 @@
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>-2.15502457985595</t>
+          <t>7.656563769672629</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>-43.05343003526515</t>
+          <t>-4.051061775258264</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>3.446587753909104</t>
+          <t>-5.436727795897101</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>73.45%</t>
+          <t>15.43%</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>-47.53%</t>
+          <t>6.21%</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
@@ -8553,32 +8553,32 @@
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>檢驗試劑87.44%、檢測設備9.39%、其他產品3.17% (2024年)</t>
+          <t>禽畜飼料51.62%、蛋品30.92%、養殖12.44%、大宗原物料買賣4.82%、其他0.19% (2024年)</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
-          <t>瑞基-農業科技業-上櫃</t>
+          <t>茂生農經-農業科技業-上櫃</t>
         </is>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>農業科技業右下</t>
+          <t>農業科技業右上</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>33.87</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>** 其他 - 農業科技業** 醫療器材 - 生物檢測</t>
+          <t>** 其他 - 農業科技業</t>
         </is>
       </c>
     </row>
@@ -8590,187 +8590,187 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>-0.71</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0.88</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>61.0</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>18.1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>-3.13</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>-0.95</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>-1.98</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>-4.16</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>57.04000000000001</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>58.19</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>60.716</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>-2.99</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>-1.11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>-1.07</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>-15.64</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>-0.39</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>-3.30</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>-3.60</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>18.17</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>18.79</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>19.492</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>-9.34</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>-0.46</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>-0.42</t>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>3.174603174603135</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>-32.37</t>
-        </is>
-      </c>
-      <c r="AG28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>747.2</t>
+          <t>453.2</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>1104.9</t>
+          <t>537.2</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-357</t>
+          <t>-84</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>-15.30216995260733</t>
+          <t>-150.299019623976</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>-34.74</t>
+          <t>-146.65</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
@@ -8780,7 +8780,7 @@
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>瑞基</t>
+          <t>茂生農經</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
@@ -8805,17 +8805,17 @@
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>-2.15502457985595</t>
+          <t>7.656563769672629</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>-43.05343003526515</t>
+          <t>-4.051061775258264</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>3.446587753909104</t>
+          <t>-5.436727795897101</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -8825,27 +8825,27 @@
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>73.45%</t>
+          <t>15.43%</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>-47.53%</t>
+          <t>6.21%</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
@@ -8855,44 +8855,44 @@
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>檢驗試劑87.44%、檢測設備9.39%、其他產品3.17% (2024年)</t>
+          <t>禽畜飼料51.62%、蛋品30.92%、養殖12.44%、大宗原物料買賣4.82%、其他0.19% (2024年)</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
-          <t>瑞基-農業科技業-上櫃</t>
+          <t>茂生農經-農業科技業-上櫃</t>
         </is>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>農業科技業右下</t>
+          <t>農業科技業右上</t>
         </is>
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>33.87</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>** 其他 - 農業科技業** 醫療器材 - 生物檢測</t>
+          <t>** 其他 - 農業科技業</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -8922,12 +8922,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -8937,142 +8937,142 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>-0.66</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>-1.88</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>-4.02</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>57.27999999999999</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>58.38</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>60.826</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>-1.60</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>-1.07</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>8.333333333333337</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>-55.96</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>-1.79</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>-4.25</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>57.0</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>58.04</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>60.614</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>35.71428571428575</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>11.90476190476192</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>16.97</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>538.4</t>
+          <t>378.6</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>460.3</t>
+          <t>859.7</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>-481</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>-148.1662574522824</t>
+          <t>-150.9617885310265</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>-136.44</t>
+          <t>-162.98</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -9204,12 +9204,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -9219,17 +9219,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -9279,57 +9279,57 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>57.04000000000001</t>
+          <t>57.48</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>58.19</t>
+          <t>58.535</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>60.716</t>
+          <t>60.924</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.333333333333337</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>-15.64</t>
+          <t>-65.36</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
@@ -9354,27 +9354,27 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>453.2</t>
+          <t>303.2</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>537.2</t>
+          <t>875.2</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-84</t>
+          <t>-572</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>-150.299019623976</t>
+          <t>-148.7771698727741</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>-146.65</t>
+          <t>-176.94</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
@@ -9424,7 +9424,7 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -9521,17 +9521,17 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -9581,62 +9581,62 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>57.27999999999999</t>
+          <t>57.64</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>58.38</t>
+          <t>58.69000000000001</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>60.826</t>
+          <t>61.018</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>-55.96</t>
+          <t>-54.30</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
@@ -9656,27 +9656,27 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>378.6</t>
+          <t>377.4</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>859.7</t>
+          <t>825.8</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-481</t>
+          <t>-448</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>-150.9617885310265</t>
+          <t>-143.6566541240782</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>-162.98</t>
+          <t>-209.64</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -9808,177 +9808,177 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>-0.87</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>57.2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>-0.90</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>-1.90</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>-3.68</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>57.72000000000001</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>58.84</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>61.08600000000001</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>-1.10</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
           <t>-1.06</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>0.31</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>57.0</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>3.030303030303074</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>-52.09</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>-0.84</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>-1.80</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>-3.92</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>57.48</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>58.535</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>60.924</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>-1.57</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>-1.08</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>-1.06</t>
-        </is>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>8.333333333333337</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>-65.36</t>
-        </is>
-      </c>
-      <c r="AG32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>303.2</t>
+          <t>382.2</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>875.2</t>
+          <t>797.8</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>-572</t>
+          <t>-415</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>-148.7771698727741</t>
+          <t>-131.6598588426528</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>-176.94</t>
+          <t>-217.79</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -10135,7 +10135,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -10145,142 +10145,142 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>-0.31</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>-1.91</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>-3.52</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>57.88</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>59.00999999999999</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>61.16</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>-3.51</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
           <t>-1.05</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>3.030303030303074</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>-26.96</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>-1.79</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>-3.82</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>57.64</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>58.69000000000001</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>61.018</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>-0.90</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>-1.06</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>8.333333333333337</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>-54.30</t>
-        </is>
-      </c>
-      <c r="AG33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>377.4</t>
+          <t>621.2</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>825.8</t>
+          <t>850.5</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>-448</t>
+          <t>-229</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>-143.6566541240782</t>
+          <t>-115.9992187108335</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>-209.64</t>
+          <t>-184.59</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
@@ -10389,1214 +10389,6 @@
         </is>
       </c>
       <c r="BH33" t="inlineStr">
-        <is>
-          <t>** 其他 - 農業科技業</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1240</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>-0.87</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>57.2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>-0.90</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>-1.90</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>-3.68</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>57.72000000000001</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>58.84</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>61.08600000000001</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>-1.10</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>-1.06</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>3.030303030303074</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>-52.09</t>
-        </is>
-      </c>
-      <c r="AG34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>382.2</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>797.8</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>-415</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>-131.6598588426528</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>-217.79</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>茂生農經</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>農業科技業</t>
-        </is>
-      </c>
-      <c r="AP34" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr">
-        <is>
-          <t>7.656563769672629</t>
-        </is>
-      </c>
-      <c r="AT34" t="inlineStr">
-        <is>
-          <t>-4.051061775258264</t>
-        </is>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>-5.436727795897101</t>
-        </is>
-      </c>
-      <c r="AV34" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>5.96</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>15.00</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>11.59</t>
-        </is>
-      </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>15.43%</t>
-        </is>
-      </c>
-      <c r="BA34" t="inlineStr">
-        <is>
-          <t>6.21%</t>
-        </is>
-      </c>
-      <c r="BB34" t="inlineStr">
-        <is>
-          <t>56.63</t>
-        </is>
-      </c>
-      <c r="BC34" t="inlineStr">
-        <is>
-          <t>2521</t>
-        </is>
-      </c>
-      <c r="BD34" t="inlineStr">
-        <is>
-          <t>禽畜飼料51.62%、蛋品30.92%、養殖12.44%、大宗原物料買賣4.82%、其他0.19% (2024年)</t>
-        </is>
-      </c>
-      <c r="BE34" t="inlineStr">
-        <is>
-          <t>茂生農經-農業科技業-上櫃</t>
-        </is>
-      </c>
-      <c r="BF34" t="inlineStr">
-        <is>
-          <t>農業科技業右上</t>
-        </is>
-      </c>
-      <c r="BG34" t="inlineStr">
-        <is>
-          <t>33.87</t>
-        </is>
-      </c>
-      <c r="BH34" t="inlineStr">
-        <is>
-          <t>** 其他 - 農業科技業</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1240</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>57.7</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>-1.23</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>-0.31</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>-1.91</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>-3.52</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>57.88</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>59.00999999999999</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>61.16</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>-3.51</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>-1.08</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>-1.05</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>3.030303030303074</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>-26.96</t>
-        </is>
-      </c>
-      <c r="AG35" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>621.2</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>850.5</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>-229</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>-115.9992187108335</t>
-        </is>
-      </c>
-      <c r="AL35" t="inlineStr">
-        <is>
-          <t>-184.59</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>茂生農經</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>農業科技業</t>
-        </is>
-      </c>
-      <c r="AP35" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr">
-        <is>
-          <t>7.656563769672629</t>
-        </is>
-      </c>
-      <c r="AT35" t="inlineStr">
-        <is>
-          <t>-4.051061775258264</t>
-        </is>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>-5.436727795897101</t>
-        </is>
-      </c>
-      <c r="AV35" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>5.96</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>15.00</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>11.59</t>
-        </is>
-      </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>15.43%</t>
-        </is>
-      </c>
-      <c r="BA35" t="inlineStr">
-        <is>
-          <t>6.21%</t>
-        </is>
-      </c>
-      <c r="BB35" t="inlineStr">
-        <is>
-          <t>56.63</t>
-        </is>
-      </c>
-      <c r="BC35" t="inlineStr">
-        <is>
-          <t>2521</t>
-        </is>
-      </c>
-      <c r="BD35" t="inlineStr">
-        <is>
-          <t>禽畜飼料51.62%、蛋品30.92%、養殖12.44%、大宗原物料買賣4.82%、其他0.19% (2024年)</t>
-        </is>
-      </c>
-      <c r="BE35" t="inlineStr">
-        <is>
-          <t>茂生農經-農業科技業-上櫃</t>
-        </is>
-      </c>
-      <c r="BF35" t="inlineStr">
-        <is>
-          <t>農業科技業右上</t>
-        </is>
-      </c>
-      <c r="BG35" t="inlineStr">
-        <is>
-          <t>33.87</t>
-        </is>
-      </c>
-      <c r="BH35" t="inlineStr">
-        <is>
-          <t>** 其他 - 農業科技業</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1240</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>57.9</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>-1.58</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>-2.12</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>-3.41</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>57.9</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>59.15499999999999</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>61.244</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>-5.71</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>-1.10</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>-1.04</t>
-        </is>
-      </c>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>9.090909090909207</t>
-        </is>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>6.951871657754103</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>24.89</t>
-        </is>
-      </c>
-      <c r="AG36" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>1340.8</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>1073.6</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>-103.5276785793199</t>
-        </is>
-      </c>
-      <c r="AL36" t="inlineStr">
-        <is>
-          <t>-143.21</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>茂生農經</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>農業科技業</t>
-        </is>
-      </c>
-      <c r="AP36" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="AQ36" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="AS36" t="inlineStr">
-        <is>
-          <t>7.656563769672629</t>
-        </is>
-      </c>
-      <c r="AT36" t="inlineStr">
-        <is>
-          <t>-4.051061775258264</t>
-        </is>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>-5.436727795897101</t>
-        </is>
-      </c>
-      <c r="AV36" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>5.96</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>15.00</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>11.59</t>
-        </is>
-      </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>15.43%</t>
-        </is>
-      </c>
-      <c r="BA36" t="inlineStr">
-        <is>
-          <t>6.21%</t>
-        </is>
-      </c>
-      <c r="BB36" t="inlineStr">
-        <is>
-          <t>56.63</t>
-        </is>
-      </c>
-      <c r="BC36" t="inlineStr">
-        <is>
-          <t>2521</t>
-        </is>
-      </c>
-      <c r="BD36" t="inlineStr">
-        <is>
-          <t>禽畜飼料51.62%、蛋品30.92%、養殖12.44%、大宗原物料買賣4.82%、其他0.19% (2024年)</t>
-        </is>
-      </c>
-      <c r="BE36" t="inlineStr">
-        <is>
-          <t>茂生農經-農業科技業-上櫃</t>
-        </is>
-      </c>
-      <c r="BF36" t="inlineStr">
-        <is>
-          <t>農業科技業右上</t>
-        </is>
-      </c>
-      <c r="BG36" t="inlineStr">
-        <is>
-          <t>33.87</t>
-        </is>
-      </c>
-      <c r="BH36" t="inlineStr">
-        <is>
-          <t>** 其他 - 農業科技業</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1240</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>57.8</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>-1.4</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>-0.48</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>-2.02</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>-3.38</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>58.08</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>59.275</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>61.348</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>-9.35</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>-1.12</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>-1.02</t>
-        </is>
-      </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>6.951871657754103</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>28.15</t>
-        </is>
-      </c>
-      <c r="AG37" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>1447.2</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>1129.3</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>-96.31209410424667</t>
-        </is>
-      </c>
-      <c r="AL37" t="inlineStr">
-        <is>
-          <t>-75.02</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>茂生農經</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>農業科技業</t>
-        </is>
-      </c>
-      <c r="AP37" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="AQ37" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="AS37" t="inlineStr">
-        <is>
-          <t>7.656563769672629</t>
-        </is>
-      </c>
-      <c r="AT37" t="inlineStr">
-        <is>
-          <t>-4.051061775258264</t>
-        </is>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>-5.436727795897101</t>
-        </is>
-      </c>
-      <c r="AV37" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>5.96</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>15.00</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>11.59</t>
-        </is>
-      </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>15.43%</t>
-        </is>
-      </c>
-      <c r="BA37" t="inlineStr">
-        <is>
-          <t>6.21%</t>
-        </is>
-      </c>
-      <c r="BB37" t="inlineStr">
-        <is>
-          <t>56.63</t>
-        </is>
-      </c>
-      <c r="BC37" t="inlineStr">
-        <is>
-          <t>2521</t>
-        </is>
-      </c>
-      <c r="BD37" t="inlineStr">
-        <is>
-          <t>禽畜飼料51.62%、蛋品30.92%、養殖12.44%、大宗原物料買賣4.82%、其他0.19% (2024年)</t>
-        </is>
-      </c>
-      <c r="BE37" t="inlineStr">
-        <is>
-          <t>茂生農經-農業科技業-上櫃</t>
-        </is>
-      </c>
-      <c r="BF37" t="inlineStr">
-        <is>
-          <t>農業科技業右上</t>
-        </is>
-      </c>
-      <c r="BG37" t="inlineStr">
-        <is>
-          <t>33.87</t>
-        </is>
-      </c>
-      <c r="BH37" t="inlineStr">
         <is>
           <t>** 其他 - 農業科技業</t>
         </is>

--- a/Result/checksun/農業科技業.xlsx
+++ b/Result/checksun/農業科技業.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>299.0</t>
+          <t>342.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -763,17 +763,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>23.71</t>
+          <t>27.12</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -798,97 +798,97 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>-9.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>342</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-7.40</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>20.34</t>
+          <t>20.38</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>21.965</t>
+          <t>21.7575</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23.138</t>
+          <t>23.088</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-32.69</t>
+          <t>-21.77</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>57.14285714285724</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2.898550724637646</t>
+          <t>19.04761904761905</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-6.96</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -898,27 +898,27 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>6100.0</t>
+          <t>5571.8</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>6138.1</t>
+          <t>5988.5</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-38</t>
+          <t>-416</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-276.2807548105715</t>
+          <t>-288.6331998259416</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>-504.75</t>
+          <t>-356.57</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -968,12 +968,12 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -998,12 +998,12 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>179.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>14.20</t>
+          <t>23.71</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1100,99 +1100,99 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>47</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>-23.0</t>
+          <t>-9.0</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>342</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-7.29</t>
+          <t>-7.40</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.34</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>22.165</t>
+          <t>21.965</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23.199</t>
+          <t>23.138</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-37.90</t>
+          <t>-32.69</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
+          <t>-0.67</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2.898550724637646</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
           <t>-0.62</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>7.863089731729819</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>-13.16</t>
-        </is>
-      </c>
       <c r="AG3" t="inlineStr">
         <is>
           <t>False</t>
@@ -1200,27 +1200,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>5370.6</t>
+          <t>6100.0</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>6184.5</t>
+          <t>6138.1</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-813</t>
+          <t>-38</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-234.7407220160158</t>
+          <t>-276.2807548105715</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>-605.41</t>
+          <t>-504.75</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>179.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1367,162 +1367,162 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>14.20</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>20.15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>-23.0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>-1.95</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>-7.29</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-4.46</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
           <t>20.55</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-3.01</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>22.165</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>23.199</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>-37.90</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>-0.85</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>-0.62</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>7.863089731729819</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>-13.16</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>-0.82</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>-7.34</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-3.76</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>20.72</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>22.3625</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>23.236</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>-44.48</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.80</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>-0.56</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>8.695652173913023</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>7.863089731729819</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>-18.59</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>5181.6</t>
+          <t>5370.6</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>6364.8</t>
+          <t>6184.5</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1183</t>
+          <t>-813</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-167.3465236768307</t>
+          <t>-234.7407220160158</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>-460.91</t>
+          <t>-605.41</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>422.0</t>
+          <t>117.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>33.47</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1689,142 +1689,142 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>-0.82</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>-7.34</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
           <t>-3.76</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>20.72</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>22.3625</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>23.236</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>-44.48</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>-0.80</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>-0.56</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>8.695652173913023</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>7.863089731729819</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>-18.59</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>-0.29</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>-7.82</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>-3.18</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>20.76</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>22.52</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>23.26</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>-57.13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>-0.78</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>-0.49</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>14.89361702127652</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>9.23804328059642</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>-6.98</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6503.8</t>
+          <t>5181.6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>6991.5</t>
+          <t>6364.8</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-487</t>
+          <t>-1183</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-113.9721704762695</t>
+          <t>-167.3465236768307</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>-113.4</t>
+          <t>-460.91</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>466.0</t>
+          <t>422.0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1971,17 +1971,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>33.47</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2016,87 +2016,87 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>79</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>342</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-7.82</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>20.76</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>22.735</t>
+          <t>22.52</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>23.27</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-76.19</t>
+          <t>-57.13</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.89361702127652</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>7.303807303807278</t>
+          <t>9.23804328059642</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-12.31</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2106,27 +2106,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6405.2</t>
+          <t>6503.8</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>7304.1</t>
+          <t>6991.5</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-898</t>
+          <t>-487</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-114.0754629947271</t>
+          <t>-113.9721704762695</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>-303.89</t>
+          <t>-113.4</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2206,12 +2206,12 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2258,177 +2258,177 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>-3.1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>466.0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-2.95</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20.35</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>-2.26</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>-8.42</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>-2.30</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>20.82</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>22.735</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>23.27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>-76.19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>-0.42</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>9.12</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-0.47</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-5.26</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>7.303807303807278</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>-12.31</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>-22.0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>-0.94</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>-7.79</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>-1.25</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>21.2</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>22.99</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>23.281</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>-92.85</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>-0.66</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>12.82051282051282</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>7.303807303807278</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>-15.01</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>6176.2</t>
+          <t>6405.2</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>7266.7</t>
+          <t>7304.1</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1090</t>
+          <t>-898</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-79.56416095700345</t>
+          <t>-114.0754629947271</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>-641.44</t>
+          <t>-303.89</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -2478,12 +2478,12 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2610,97 +2610,97 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>53</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>342</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-7.79</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>23.185</t>
+          <t>22.99</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>23.278</t>
+          <t>23.281</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-131.38</t>
+          <t>-92.85</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>9.090909090909092</t>
+          <t>12.82051282051282</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3.030303030303002</t>
+          <t>7.303807303807278</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-15.01</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -2710,27 +2710,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>6998.4</t>
+          <t>6176.2</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>7315.0</t>
+          <t>7266.7</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-316</t>
+          <t>-1090</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>22.59500689859151</t>
+          <t>-79.56416095700345</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>-334.03</t>
+          <t>-641.44</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
@@ -2847,12 +2847,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>437.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2877,17 +2877,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>34.66</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2937,72 +2937,72 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>342</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-6.49</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>23.3875</t>
+          <t>23.185</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>23.276</t>
+          <t>23.278</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-201.99</t>
+          <t>-131.38</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.090909090909092</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.030303030303002</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -3012,27 +3012,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>7548.0</t>
+          <t>6998.4</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>8143.3</t>
+          <t>7315.0</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-595</t>
+          <t>-316</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>87.43661315819058</t>
+          <t>22.59500689859151</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>94.23</t>
+          <t>-334.03</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3164,12 +3164,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>392.0</t>
+          <t>437.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3179,17 +3179,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>31.09</t>
+          <t>34.66</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -3239,57 +3239,57 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>342</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-6.49</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>23.6025</t>
+          <t>23.3875</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>23.26899999999999</t>
+          <t>23.276</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-362.37</t>
+          <t>-201.99</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3.50877192982446</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-6.74</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -3314,27 +3314,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>7479.2</t>
+          <t>7548.0</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>8019.4</t>
+          <t>8143.3</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-540</t>
+          <t>-595</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>86.20225112166432</t>
+          <t>87.43661315819058</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>94.23</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -3384,12 +3384,12 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3481,17 +3481,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -3536,52 +3536,52 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>43</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>24.33</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>24.505</t>
+          <t>24.4825</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>25.306</t>
+          <t>25.258</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>11.40</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -3591,22 +3591,22 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>20.00000000000028</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>24.84848484848476</t>
+          <t>15.75757575757576</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -3616,27 +3616,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1097.8</t>
+          <t>897.8</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>971.8</t>
+          <t>954.1</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>-56</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-30.09537599446625</t>
+          <t>-31.80781694108194</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>-56.31</t>
+          <t>-41.23</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3661,12 +3661,12 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -3686,12 +3686,12 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>101.46</t>
+          <t>100.83</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3768,177 +3768,177 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>6.92</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>24.35</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>-0.62</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>13.15</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>24.4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>-11.0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>-0.71</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>-3.17</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>24.33</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>24.505</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>25.306</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>11.40</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>-0.30</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>20.00000000000028</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>24.84848484848476</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>12.97</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>-16.0</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>-0.72</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>-3.28</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>24.34</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>24.5175</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>25.35</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>10.77</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>-0.31</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>27.27272727272697</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>18.18181818181799</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>20.90</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1181.2</t>
+          <t>1097.8</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>977.0</t>
+          <t>971.8</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-25.32931992241485</t>
+          <t>-30.09537599446625</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>-16.27</t>
+          <t>-56.31</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>101.46</t>
+          <t>100.83</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
@@ -4018,12 +4018,12 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>13.15</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -4130,72 +4130,72 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>42</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-16.0</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>43</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>24.37</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>24.5625</t>
+          <t>24.5175</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>25.398</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>9.090909090909001</t>
+          <t>18.18181818181799</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>20.90</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -4220,27 +4220,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1199.2</t>
+          <t>1181.2</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>931.3</t>
+          <t>977.0</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>204</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-26.97600037401336</t>
+          <t>-25.32931992241485</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-16.27</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -4265,12 +4265,12 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>101.46</t>
+          <t>100.83</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4372,12 +4372,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -4427,42 +4427,42 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>58</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>43</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -4472,27 +4472,27 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.37</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>24.61</t>
+          <t>24.5625</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>25.446</t>
+          <t>25.398</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -4502,17 +4502,17 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27272727272697</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.090909090909001</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>14.20</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -4522,27 +4522,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1097.2</t>
+          <t>1199.2</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>960.8</t>
+          <t>931.3</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-30.95270620332881</t>
+          <t>-26.97600037401336</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>-5.1</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -4592,12 +4592,12 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>101.46</t>
+          <t>100.83</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>29.07</t>
+          <t>17.99</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>59</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -4744,52 +4744,52 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>43</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>24.665</t>
+          <t>24.61</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>25.498</t>
+          <t>25.446</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>12.50000000000012</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>12.63</t>
+          <t>14.20</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -4824,27 +4824,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1010.4</t>
+          <t>1097.2</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>897.1</t>
+          <t>960.8</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>136</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-40.67090714022483</t>
+          <t>-30.95270620332881</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>12.16</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>101.46</t>
+          <t>100.83</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4991,17 +4991,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>29.07</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>55</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -5046,64 +5046,64 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>43</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>-3.27</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>24.53</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>24.665</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>25.498</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>9.63</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>-0.30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
           <t>-0.33</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>-3.24</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>24.64</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>24.7225</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>25.55</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>14.34</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>-0.29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
       <c r="AD16" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -5111,12 +5111,12 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>37.50000000000005</t>
+          <t>12.50000000000012</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>12.63</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -5126,27 +5126,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>845.8</t>
+          <t>1010.4</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>831.6</t>
+          <t>897.1</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-50.27659455620269</t>
+          <t>-40.67090714022483</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>-85.65</t>
+          <t>12.16</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>101.46</t>
+          <t>100.83</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
@@ -5226,12 +5226,12 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -5348,52 +5348,52 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>43</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>24.66</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>24.7675</t>
+          <t>24.7225</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>25.599</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>14.34</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -5403,22 +5403,22 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>37.50000000000033</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>66.66666666666667</t>
+          <t>37.50000000000005</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -5428,27 +5428,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>772.8</t>
+          <t>845.8</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>796.7</t>
+          <t>831.6</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-23</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-43.8453849716733</t>
+          <t>-50.27659455620269</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>-100.28</t>
+          <t>-85.65</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>101.46</t>
+          <t>100.83</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -5595,17 +5595,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -5655,72 +5655,72 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>43</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>24.66</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>24.81</t>
+          <t>24.7675</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>25.647</t>
+          <t>25.599</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>17.74</t>
+          <t>17.32</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>74.99999999999977</t>
+          <t>37.50000000000033</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>87.49999999999989</t>
+          <t>66.66666666666667</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>-16.93</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -5730,27 +5730,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>663.4</t>
+          <t>772.8</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>798.6</t>
+          <t>796.7</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-135</t>
+          <t>-23</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-33.58449708943989</t>
+          <t>-43.8453849716733</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>-129.17</t>
+          <t>-100.28</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>101.46</t>
+          <t>100.83</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -5897,17 +5897,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -5957,72 +5957,72 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>43</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>24.58</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>24.8425</t>
+          <t>24.81</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>25.683</t>
+          <t>25.647</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>17.74</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
+          <t>74.99999999999977</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
           <t>87.49999999999989</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>79.16666666666664</t>
-        </is>
-      </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-16.93</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -6032,27 +6032,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>824.4</t>
+          <t>663.4</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>859.5</t>
+          <t>798.6</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-35</t>
+          <t>-135</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-16.20474274946435</t>
+          <t>-33.58449708943989</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>-90.09</t>
+          <t>-129.17</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>101.46</t>
+          <t>100.83</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -6199,17 +6199,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -6259,47 +6259,47 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>19</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.28</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>17.93</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>19.033</t>
+          <t>18.988</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -6309,22 +6309,22 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.18181818181809</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2.564102564102625</t>
+          <t>6.060606060606051</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>-23.28</t>
+          <t>-23.86</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -6334,27 +6334,27 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>907.4</t>
+          <t>848.6</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1182.7</t>
+          <t>1114.5</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-275</t>
+          <t>-265</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>21.74097501231918</t>
+          <t>10.74262987655996</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>-49.75</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -6501,17 +6501,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -6561,57 +6561,57 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>19</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-5.46</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>18.04</t>
+          <t>17.93</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19.082</t>
+          <t>19.033</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>-23.28</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -6636,27 +6636,27 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1205.0</t>
+          <t>907.4</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1148.7</t>
+          <t>1182.7</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-275</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>24.01367745167646</t>
+          <t>21.74097501231918</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>-26.39</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -6788,12 +6788,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -6803,17 +6803,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -6853,82 +6853,82 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>19</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-5.46</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>17.61</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>18.1475</t>
+          <t>18.04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19.127</t>
+          <t>19.082</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>7.692307692307819</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>4.945054945055042</t>
+          <t>2.564102564102625</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>13.50</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -6938,27 +6938,27 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1320.8</t>
+          <t>1205.0</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1163.7</t>
+          <t>1148.7</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>33.17794860050819</t>
+          <t>24.01367745167646</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>26.62</t>
+          <t>-26.39</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
@@ -7038,12 +7038,12 @@
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -7090,32 +7090,32 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>47.0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>-0.28</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>0.29</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -7145,67 +7145,67 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>19</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>17.71</t>
+          <t>17.61</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>18.24</t>
+          <t>18.1475</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19.168</t>
+          <t>19.127</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -7220,17 +7220,17 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.692307692307819</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2.380952380952436</t>
+          <t>4.945054945055042</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>16.57</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -7240,27 +7240,27 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1355.6</t>
+          <t>1320.8</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1162.9</t>
+          <t>1163.7</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>157</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>34.37109505330403</t>
+          <t>33.17794860050819</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>65.07</t>
+          <t>26.62</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
@@ -7340,12 +7340,12 @@
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -7407,17 +7407,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -7457,7 +7457,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -7467,47 +7467,47 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>19</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>17.84</t>
+          <t>17.71</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>18.335</t>
+          <t>18.24</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19.212</t>
+          <t>19.168</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>7.142857142857252</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>16.57</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -7542,27 +7542,27 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>1380.4</t>
+          <t>1355.6</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>1099.5</t>
+          <t>1162.9</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>28.79025101718597</t>
+          <t>34.37109505330403</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>79.21</t>
+          <t>65.07</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -7749,7 +7749,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -7759,62 +7759,62 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>19</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.84</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>18.4325</t>
+          <t>18.335</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19.263</t>
+          <t>19.212</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -7824,17 +7824,17 @@
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.142857142857252</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.380952380952436</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>32.23</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -7844,27 +7844,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>1458.0</t>
+          <t>1380.4</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>1102.6</t>
+          <t>1099.5</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>280</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>19.6236819068325</t>
+          <t>28.79025101718597</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>156.47</t>
+          <t>79.21</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
@@ -7981,12 +7981,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -8011,162 +8011,162 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
+          <t>17.5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>-2.04</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>-2.51</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>-2.62</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>-4.31</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
           <t>17.95</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>-5.9</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>18.4325</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>19.263</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>-4.06</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>32.23</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>-0.66</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>-2.50</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>-4.05</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>18.07</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>18.5325</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>19.315</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>-0.43</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>-0.43</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>11.1111111111106</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>25.36</t>
-        </is>
-      </c>
-      <c r="AG26" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>1092.4</t>
+          <t>1458.0</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>871.4</t>
+          <t>1102.6</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>355</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>-5.257713884383525</t>
+          <t>19.6236819068325</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>156.47</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -8298,12 +8298,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -8313,17 +8313,17 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -8333,7 +8333,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-6.49</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -8373,47 +8373,47 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>19</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.07</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>18.5325</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>19.361</t>
+          <t>19.315</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>25.36</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -8448,27 +8448,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>1006.6</t>
+          <t>1092.4</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>822.9</t>
+          <t>871.4</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>221</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>-8.715777394892697</t>
+          <t>-5.257713884383525</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
@@ -8585,12 +8585,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -8600,12 +8600,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -8615,17 +8615,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -8635,7 +8635,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -8675,52 +8675,52 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>19</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>19.394</t>
+          <t>19.361</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -8730,7 +8730,7 @@
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>33.33333333333176</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -8750,27 +8750,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>970.2</t>
+          <t>1006.6</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>871.0</t>
+          <t>822.9</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>183</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>-12.07432927856225</t>
+          <t>-8.715777394892697</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
@@ -8892,7 +8892,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -8902,12 +8902,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -8917,17 +8917,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -8977,72 +8977,72 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>56.82000000000001</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>57.73</t>
+          <t>57.59499999999999</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>60.398</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>16.66666666666686</t>
+          <t>27.27272727272697</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>29.36507936507946</t>
+          <t>26.55122655122653</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
@@ -9052,27 +9052,27 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>497.8</t>
+          <t>610.4</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>400.5</t>
+          <t>494.5</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>-143.6106283060014</t>
+          <t>-130.186025106851</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>-110.45</t>
+          <t>-56.35</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>11.54</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
@@ -9152,12 +9152,12 @@
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -9204,177 +9204,177 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>-0.52</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-1.41</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>56.7</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>57.0</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>-0.53</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>-1.58</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>-4.42</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>56.82000000000001</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>57.73</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>60.398</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>-1.06</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>16.66666666666686</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>29.36507936507946</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>24.29</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>-1.75</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>-4.31</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>56.88</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>57.895</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>60.504</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>3.07</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>-1.03</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>35.71428571428575</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>23.80952380952384</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>10.86</t>
-        </is>
-      </c>
-      <c r="AG30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>469.4</t>
+          <t>497.8</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>423.4</t>
+          <t>400.5</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>-149.6403341951938</t>
+          <t>-143.6106283060014</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>-157.75</t>
+          <t>-110.45</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>11.54</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
@@ -9454,12 +9454,12 @@
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -9581,59 +9581,59 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>56.88</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>57.895</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>60.614</t>
+          <t>60.504</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
+          <t>-1.03</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
           <t>-1.07</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
       <c r="AD31" t="inlineStr">
         <is>
           <t>35.71428571428575</t>
@@ -9641,12 +9641,12 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>11.90476190476192</t>
+          <t>23.80952380952384</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
@@ -9656,27 +9656,27 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>538.4</t>
+          <t>469.4</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>460.3</t>
+          <t>423.4</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>-148.1662574522824</t>
+          <t>-149.6403341951938</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>-136.44</t>
+          <t>-157.75</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>11.54</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
@@ -9793,12 +9793,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -9823,162 +9823,162 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>-1.79</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>-4.25</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>58.04</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>60.614</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>-1.07</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>-1.07</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>35.71428571428575</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>11.90476190476192</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>16.97</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>-0.95</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>-1.98</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>-4.16</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>57.04000000000001</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>58.19</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>60.716</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>-2.99</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>-1.11</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>-15.64</t>
-        </is>
-      </c>
-      <c r="AG32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>453.2</t>
+          <t>538.4</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>537.2</t>
+          <t>460.3</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>-84</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>-150.299019623976</t>
+          <t>-148.1662574522824</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>-146.65</t>
+          <t>-136.44</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>11.54</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
@@ -10058,12 +10058,12 @@
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -10125,17 +10125,17 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -10185,52 +10185,52 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>57.27999999999999</t>
+          <t>57.04000000000001</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>58.38</t>
+          <t>58.19</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>60.826</t>
+          <t>60.716</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>8.333333333333337</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>-55.96</t>
+          <t>-15.64</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
@@ -10260,27 +10260,27 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>378.6</t>
+          <t>453.2</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>859.7</t>
+          <t>537.2</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>-481</t>
+          <t>-84</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>-150.9617885310265</t>
+          <t>-150.299019623976</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>-162.98</t>
+          <t>-146.65</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
@@ -10330,12 +10330,12 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
@@ -10345,7 +10345,7 @@
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>11.54</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -10412,12 +10412,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -10427,17 +10427,17 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -10467,7 +10467,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -10487,47 +10487,47 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>57.48</t>
+          <t>57.27999999999999</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>58.535</t>
+          <t>58.38</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>60.924</t>
+          <t>60.826</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>-65.36</t>
+          <t>-55.96</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
@@ -10562,27 +10562,27 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>303.2</t>
+          <t>378.6</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>875.2</t>
+          <t>859.7</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>-572</t>
+          <t>-481</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>-148.7771698727741</t>
+          <t>-150.9617885310265</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>-176.94</t>
+          <t>-162.98</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -10607,7 +10607,7 @@
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>11.54</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
@@ -10662,12 +10662,12 @@
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
@@ -10704,7 +10704,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -10729,7 +10729,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -10739,7 +10739,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -10769,7 +10769,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -10779,74 +10779,74 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>-1.80</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>-3.92</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>57.48</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>58.535</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>60.924</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>-1.06</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>-1.79</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>-3.82</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>57.64</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>58.69000000000001</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>61.018</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>-0.90</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>-1.06</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
       <c r="AE35" t="inlineStr">
         <is>
           <t>8.333333333333337</t>
@@ -10854,7 +10854,7 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>-54.30</t>
+          <t>-65.36</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
@@ -10864,27 +10864,27 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>377.4</t>
+          <t>303.2</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>825.8</t>
+          <t>875.2</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>-448</t>
+          <t>-572</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>-143.6566541240782</t>
+          <t>-148.7771698727741</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>-209.64</t>
+          <t>-176.94</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
@@ -10934,12 +10934,12 @@
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>11.54</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
@@ -11006,7 +11006,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -11031,17 +11031,17 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -11091,52 +11091,52 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>-1.79</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>-3.82</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>57.64</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>58.69000000000001</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>61.018</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
           <t>-0.90</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>-1.90</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>-3.68</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>57.72000000000001</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>58.84</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>61.08600000000001</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -11146,17 +11146,17 @@
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>3.030303030303074</t>
+          <t>8.333333333333337</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>-52.09</t>
+          <t>-54.30</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
@@ -11166,27 +11166,27 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>382.2</t>
+          <t>377.4</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>797.8</t>
+          <t>825.8</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>-415</t>
+          <t>-448</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>-131.6598588426528</t>
+          <t>-143.6566541240782</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>-217.79</t>
+          <t>-209.64</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
@@ -11236,12 +11236,12 @@
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>11.54</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -11318,12 +11318,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -11353,7 +11353,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -11393,57 +11393,57 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>57.88</t>
+          <t>57.72000000000001</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>59.00999999999999</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>61.16</t>
+          <t>61.08600000000001</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>-26.96</t>
+          <t>-52.09</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
@@ -11468,27 +11468,27 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>621.2</t>
+          <t>382.2</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>850.5</t>
+          <t>797.8</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>-229</t>
+          <t>-415</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>-115.9992187108335</t>
+          <t>-131.6598588426528</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>-184.59</t>
+          <t>-217.79</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
@@ -11538,12 +11538,12 @@
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>11.54</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="BD37" t="inlineStr">

--- a/Result/checksun/農業科技業.xlsx
+++ b/Result/checksun/農業科技業.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>342.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -763,17 +763,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>27.12</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -803,92 +803,92 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>54</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>43</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>20.34</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>21.7575</t>
+          <t>21.61</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23.088</t>
+          <t>23.032</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-21.77</t>
+          <t>-13.93</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>57.14285714285724</t>
+          <t>52.38095238095242</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>19.04761904761905</t>
+          <t>36.50793650793653</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-6.96</t>
+          <t>-24.14</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -898,27 +898,27 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>5571.8</t>
+          <t>3974.6</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>5988.5</t>
+          <t>5239.2</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-416</t>
+          <t>-1264</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-288.6331998259416</t>
+          <t>-351.6445313582752</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>-356.57</t>
+          <t>-698.21</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -998,12 +998,12 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>299.0</t>
+          <t>342.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>23.71</t>
+          <t>27.12</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1105,92 +1105,92 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>-9.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>43</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-7.40</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>20.34</t>
+          <t>20.38</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>21.965</t>
+          <t>21.7575</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23.138</t>
+          <t>23.088</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-32.69</t>
+          <t>-21.77</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>57.14285714285724</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2.898550724637646</t>
+          <t>19.04761904761905</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-6.96</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1200,27 +1200,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>6100.0</t>
+          <t>5571.8</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>6138.1</t>
+          <t>5988.5</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-38</t>
+          <t>-416</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-276.2807548105715</t>
+          <t>-288.6331998259416</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>-504.75</t>
+          <t>-356.57</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>179.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1367,17 +1367,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14.20</t>
+          <t>23.71</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1387,199 +1387,199 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>-9.0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>-1.92</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>-7.40</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-5.07</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>20.34</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>21.965</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>23.138</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>-32.69</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>-0.89</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>-0.67</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2.898550724637646</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>-0.62</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>6100.0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>6138.1</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>-38</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>-276.2807548105715</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>-504.75</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>達邦蛋白</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>農業科技業</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>-31.27243717590746</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-20.91614265387616</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>-16.94616644850042</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>1.95</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>-23.0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>-1.95</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>-7.29</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-4.46</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>22.165</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>23.199</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>-37.90</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.85</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>-0.62</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>7.863089731729819</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>-13.16</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>5370.6</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>6184.5</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>-813</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>-234.7407220160158</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>-605.41</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>達邦蛋白</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>農業科技業</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>-31.27243717590746</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-20.91614265387616</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>-16.94616644850042</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
       <c r="AX4" t="inlineStr">
         <is>
           <t>1.26</t>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>179.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1669,162 +1669,162 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>14.20</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>20.15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>-23.0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>-1.95</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>-7.29</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-4.46</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
           <t>20.55</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>22.165</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>23.199</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>-37.90</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>-0.85</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>-0.62</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>7.863089731729819</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>-13.16</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>-0.82</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>-7.34</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>-3.76</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>20.72</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>22.3625</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>23.236</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>-44.48</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>-0.80</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>-0.56</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>8.695652173913023</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>7.863089731729819</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>-18.59</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5181.6</t>
+          <t>5370.6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>6364.8</t>
+          <t>6184.5</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1183</t>
+          <t>-813</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-167.3465236768307</t>
+          <t>-234.7407220160158</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>-460.91</t>
+          <t>-605.41</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>422.0</t>
+          <t>117.0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1971,17 +1971,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>33.47</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -2021,82 +2021,82 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>43</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-7.82</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>22.3625</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>23.236</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-57.13</t>
+          <t>-44.48</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>14.89361702127652</t>
+          <t>8.695652173913023</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>9.23804328059642</t>
+          <t>7.863089731729819</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>-18.59</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2106,27 +2106,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6503.8</t>
+          <t>5181.6</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>6991.5</t>
+          <t>6364.8</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-487</t>
+          <t>-1183</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-113.9721704762695</t>
+          <t>-167.3465236768307</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>-113.4</t>
+          <t>-460.91</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -2206,12 +2206,12 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>466.0</t>
+          <t>422.0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2273,17 +2273,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>33.47</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2318,87 +2318,87 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>79</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>43</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-7.82</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>20.76</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>22.735</t>
+          <t>22.52</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>23.27</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-76.19</t>
+          <t>-57.13</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.89361702127652</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>7.303807303807278</t>
+          <t>9.23804328059642</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-12.31</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -2408,27 +2408,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>6405.2</t>
+          <t>6503.8</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>7304.1</t>
+          <t>6991.5</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-898</t>
+          <t>-487</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-114.0754629947271</t>
+          <t>-113.9721704762695</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>-303.89</t>
+          <t>-113.4</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2560,177 +2560,177 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>-3.1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>466.0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-2.95</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20.35</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>56.0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>-2.26</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>-8.42</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>-2.30</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>20.82</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>22.735</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>23.27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>-76.19</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>-0.42</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>9.12</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-0.47</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>-2.19</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>7.303807303807278</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>-12.31</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>53.0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>-0.94</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>-7.79</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>-1.25</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>21.2</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>22.99</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>23.281</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>-92.85</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>-0.66</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>12.82051282051282</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>7.303807303807278</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>-15.01</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>6176.2</t>
+          <t>6405.2</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>7266.7</t>
+          <t>7304.1</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1090</t>
+          <t>-898</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-79.56416095700345</t>
+          <t>-114.0754629947271</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>-641.44</t>
+          <t>-303.89</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2937,72 +2937,72 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>43</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-7.79</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>23.185</t>
+          <t>22.99</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>23.278</t>
+          <t>23.281</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-131.38</t>
+          <t>-92.85</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>9.090909090909092</t>
+          <t>12.82051282051282</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3.030303030303002</t>
+          <t>7.303807303807278</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-15.01</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -3012,27 +3012,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6998.4</t>
+          <t>6176.2</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>7315.0</t>
+          <t>7266.7</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-316</t>
+          <t>-1090</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>22.59500689859151</t>
+          <t>-79.56416095700345</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>-334.03</t>
+          <t>-641.44</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
@@ -3149,12 +3149,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3164,12 +3164,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>437.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3179,17 +3179,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>34.66</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -3239,72 +3239,72 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>43</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-6.49</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>23.3875</t>
+          <t>23.185</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>23.276</t>
+          <t>23.278</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-201.99</t>
+          <t>-131.38</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.090909090909092</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.030303030303002</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -3314,27 +3314,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>7548.0</t>
+          <t>6998.4</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>8143.3</t>
+          <t>7315.0</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-595</t>
+          <t>-316</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>87.43661315819058</t>
+          <t>22.59500689859151</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>94.23</t>
+          <t>-334.03</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>15.22</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -3541,47 +3541,47 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>24.31</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>24.4825</t>
+          <t>24.4625</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>25.258</t>
+          <t>25.207</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -3601,12 +3601,12 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>15.75757575757576</t>
+          <t>6.666666666666771</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-12.14</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -3616,27 +3616,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>897.8</t>
+          <t>859.6</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>954.1</t>
+          <t>978.4</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-56</t>
+          <t>-118</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-31.80781694108194</t>
+          <t>-31.03551841529782</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>-41.23</t>
+          <t>-26.79</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3783,17 +3783,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -3838,52 +3838,52 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>24.33</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>24.505</t>
+          <t>24.4825</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>25.306</t>
+          <t>25.258</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>11.40</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -3893,22 +3893,22 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>20.00000000000028</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>24.84848484848476</t>
+          <t>15.75757575757576</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -3918,27 +3918,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1097.8</t>
+          <t>897.8</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>971.8</t>
+          <t>954.1</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>-56</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-30.09537599446625</t>
+          <t>-31.80781694108194</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>-56.31</t>
+          <t>-41.23</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4070,177 +4070,177 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>6.92</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>24.35</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>-0.62</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>13.15</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>24.4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>-0.83</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>-11.0</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>-0.71</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>-3.17</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>24.33</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>24.505</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>25.306</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>11.40</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>-0.30</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>20.00000000000028</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>24.84848484848476</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>12.97</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>-16.0</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>-0.72</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>-3.28</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>24.34</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>24.5175</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>25.35</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>10.77</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>-0.31</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>27.27272727272697</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>18.18181818181799</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>20.90</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1181.2</t>
+          <t>1097.8</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>977.0</t>
+          <t>971.8</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-25.32931992241485</t>
+          <t>-30.09537599446625</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>-16.27</t>
+          <t>-56.31</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4372,12 +4372,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>13.15</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4432,72 +4432,72 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>42</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-16.0</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>24.37</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>24.5625</t>
+          <t>24.5175</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>25.398</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>9.090909090909001</t>
+          <t>18.18181818181799</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>20.90</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -4522,27 +4522,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1199.2</t>
+          <t>1181.2</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>931.3</t>
+          <t>977.0</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>204</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-26.97600037401336</t>
+          <t>-25.32931992241485</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-16.27</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4567,12 +4567,12 @@
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -4729,42 +4729,42 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>58</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -4774,27 +4774,27 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.37</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>24.61</t>
+          <t>24.5625</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>25.446</t>
+          <t>25.398</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -4804,17 +4804,17 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27272727272697</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.090909090909001</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>14.20</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -4824,27 +4824,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1097.2</t>
+          <t>1199.2</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>960.8</t>
+          <t>931.3</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-30.95270620332881</t>
+          <t>-26.97600037401336</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>-5.1</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4976,12 +4976,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>29.07</t>
+          <t>17.99</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>59</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -5046,52 +5046,52 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>24.665</t>
+          <t>24.61</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>25.498</t>
+          <t>25.446</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>12.50000000000012</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>12.63</t>
+          <t>14.20</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -5126,27 +5126,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1010.4</t>
+          <t>1097.2</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>897.1</t>
+          <t>960.8</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>136</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-40.67090714022483</t>
+          <t>-30.95270620332881</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>12.16</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>29.07</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>55</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -5348,64 +5348,64 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>-3.27</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>24.53</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>24.665</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>25.498</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>9.63</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>-0.30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
           <t>-0.33</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>-3.24</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>24.64</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>24.7225</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>25.55</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>14.34</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>-0.29</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
       <c r="AD17" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -5413,12 +5413,12 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>37.50000000000005</t>
+          <t>12.50000000000012</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>12.63</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -5428,27 +5428,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>845.8</t>
+          <t>1010.4</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>831.6</t>
+          <t>897.1</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-50.27659455620269</t>
+          <t>-40.67090714022483</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>-85.65</t>
+          <t>12.16</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -5595,17 +5595,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -5655,47 +5655,47 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>24.66</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>24.7675</t>
+          <t>24.7225</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>25.599</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>14.34</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -5705,22 +5705,22 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>37.50000000000033</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>66.66666666666667</t>
+          <t>37.50000000000005</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -5730,27 +5730,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>772.8</t>
+          <t>845.8</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>796.7</t>
+          <t>831.6</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-23</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-43.8453849716733</t>
+          <t>-50.27659455620269</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>-100.28</t>
+          <t>-85.65</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -5897,17 +5897,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -5957,72 +5957,72 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>24.66</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>24.81</t>
+          <t>24.7675</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>25.647</t>
+          <t>25.599</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>17.74</t>
+          <t>17.32</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>74.99999999999977</t>
+          <t>37.50000000000033</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>87.49999999999989</t>
+          <t>66.66666666666667</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>-16.93</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -6032,27 +6032,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>663.4</t>
+          <t>772.8</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>798.6</t>
+          <t>796.7</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-135</t>
+          <t>-23</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-33.58449708943989</t>
+          <t>-43.8453849716733</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>-129.17</t>
+          <t>-100.28</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -6199,17 +6199,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -6259,47 +6259,47 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>17.28</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>17.81</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18.988</t>
+          <t>18.927</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -6309,22 +6309,22 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>18.18181818181809</t>
+          <t>15.00000000000021</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>6.060606060606051</t>
+          <t>11.06060606060612</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>-23.86</t>
+          <t>-31.34</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -6334,27 +6334,27 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>848.6</t>
+          <t>708.6</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1114.5</t>
+          <t>1032.1</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-265</t>
+          <t>-323</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>10.74262987655996</t>
+          <t>-2.959640510147992</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>-49.75</t>
+          <t>-78.32</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -6501,17 +6501,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -6561,47 +6561,47 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.28</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>17.93</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19.033</t>
+          <t>18.988</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -6611,22 +6611,22 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.18181818181809</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2.564102564102625</t>
+          <t>6.060606060606051</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>-23.28</t>
+          <t>-23.86</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -6636,27 +6636,27 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>907.4</t>
+          <t>848.6</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1182.7</t>
+          <t>1114.5</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-275</t>
+          <t>-265</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>21.74097501231918</t>
+          <t>10.74262987655996</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>-49.75</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -6788,12 +6788,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -6803,17 +6803,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -6863,57 +6863,57 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-5.46</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>18.04</t>
+          <t>17.93</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19.082</t>
+          <t>19.033</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>-23.28</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -6938,27 +6938,27 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1205.0</t>
+          <t>907.4</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1148.7</t>
+          <t>1182.7</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-275</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>24.01367745167646</t>
+          <t>21.74097501231918</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>-26.39</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
@@ -7038,12 +7038,12 @@
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -7090,12 +7090,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -7105,17 +7105,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -7155,82 +7155,82 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-5.46</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>17.61</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>18.1475</t>
+          <t>18.04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19.127</t>
+          <t>19.082</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>7.692307692307819</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>4.945054945055042</t>
+          <t>2.564102564102625</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>13.50</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -7240,27 +7240,27 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1320.8</t>
+          <t>1205.0</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1163.7</t>
+          <t>1148.7</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>33.17794860050819</t>
+          <t>24.01367745167646</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>26.62</t>
+          <t>-26.39</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
@@ -7340,12 +7340,12 @@
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -7392,32 +7392,32 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>47.0</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>-0.28</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>0.29</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -7447,67 +7447,67 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>17.71</t>
+          <t>17.61</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>18.24</t>
+          <t>18.1475</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19.168</t>
+          <t>19.127</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -7522,17 +7522,17 @@
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.692307692307819</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2.380952380952436</t>
+          <t>4.945054945055042</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>16.57</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -7542,27 +7542,27 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>1355.6</t>
+          <t>1320.8</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>1162.9</t>
+          <t>1163.7</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>157</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>34.37109505330403</t>
+          <t>33.17794860050819</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>65.07</t>
+          <t>26.62</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -7709,17 +7709,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -7769,47 +7769,47 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>17.84</t>
+          <t>17.71</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>18.335</t>
+          <t>18.24</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19.212</t>
+          <t>19.168</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>7.142857142857252</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
@@ -7834,7 +7834,7 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>16.57</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -7844,27 +7844,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>1380.4</t>
+          <t>1355.6</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>1099.5</t>
+          <t>1162.9</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>28.79025101718597</t>
+          <t>34.37109505330403</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>79.21</t>
+          <t>65.07</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -8071,52 +8071,52 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.84</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>18.4325</t>
+          <t>18.335</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19.263</t>
+          <t>19.212</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -8126,17 +8126,17 @@
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.142857142857252</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.380952380952436</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>32.23</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -8146,27 +8146,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>1458.0</t>
+          <t>1380.4</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>1102.6</t>
+          <t>1099.5</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>280</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>19.6236819068325</t>
+          <t>28.79025101718597</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>156.47</t>
+          <t>79.21</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
@@ -8283,12 +8283,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -8298,12 +8298,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -8313,162 +8313,162 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
+          <t>17.5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>-2.34</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>-2.51</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>-2.62</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>-4.31</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
           <t>17.95</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>-4.66</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>18.4325</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>19.263</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>-4.06</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>32.23</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>-0.66</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>-2.50</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>-4.05</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>18.07</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>18.5325</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>19.315</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>-0.43</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>-0.43</t>
-        </is>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>11.1111111111106</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>25.36</t>
-        </is>
-      </c>
-      <c r="AG27" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>1092.4</t>
+          <t>1458.0</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>871.4</t>
+          <t>1102.6</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>355</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>-5.257713884383525</t>
+          <t>19.6236819068325</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>156.47</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
@@ -8590,7 +8590,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -8600,12 +8600,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -8615,17 +8615,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -8635,7 +8635,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -8675,47 +8675,47 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.07</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>18.5325</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>19.361</t>
+          <t>19.315</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>25.36</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -8750,27 +8750,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>1006.6</t>
+          <t>1092.4</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>822.9</t>
+          <t>871.4</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>221</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>-8.715777394892697</t>
+          <t>-5.257713884383525</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
@@ -8892,7 +8892,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -8902,177 +8902,177 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
           <t>0.18</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>56.8</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>-1.10</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>-4.45</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>56.9</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>57.535</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>60.216</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>8.95</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>-0.93</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>-1.02</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>45.4545454545454</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>29.79797979797975</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>11.08</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>-1.38</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>-4.49</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>56.8</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>57.59499999999999</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>60.3</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>5.77</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>-0.98</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>-1.04</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>27.27272727272697</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>26.55122655122653</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>23.44</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>610.4</t>
+          <t>566.2</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>494.5</t>
+          <t>509.7</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>-130.186025106851</t>
+          <t>-121.4496155428726</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>-56.35</t>
+          <t>-73.4</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>11.54</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
@@ -9152,12 +9152,12 @@
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -9204,12 +9204,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -9219,17 +9219,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -9279,72 +9279,72 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>6</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>56.82000000000001</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>57.73</t>
+          <t>57.59499999999999</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>60.398</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>16.66666666666686</t>
+          <t>27.27272727272697</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>29.36507936507946</t>
+          <t>26.55122655122653</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
@@ -9354,27 +9354,27 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>497.8</t>
+          <t>610.4</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>400.5</t>
+          <t>494.5</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>-143.6106283060014</t>
+          <t>-130.186025106851</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>-110.45</t>
+          <t>-56.35</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>11.54</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
@@ -9454,12 +9454,12 @@
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -9506,177 +9506,177 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>-0.52</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-1.41</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>56.7</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>57.0</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>-1.58</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>-4.42</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>56.82000000000001</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>57.73</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>60.398</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>-1.06</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>16.66666666666686</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>29.36507936507946</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>24.29</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>-1.75</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>-4.31</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>56.88</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>57.895</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>60.504</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>3.07</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>-1.03</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>35.71428571428575</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>23.80952380952384</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>10.86</t>
-        </is>
-      </c>
-      <c r="AG31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>469.4</t>
+          <t>497.8</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>423.4</t>
+          <t>400.5</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>-149.6403341951938</t>
+          <t>-143.6106283060014</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>-157.75</t>
+          <t>-110.45</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
@@ -9726,12 +9726,12 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>11.54</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -9823,12 +9823,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -9883,59 +9883,59 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>6</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>56.88</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>57.895</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>60.614</t>
+          <t>60.504</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
+          <t>-1.03</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
           <t>-1.07</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
       <c r="AD32" t="inlineStr">
         <is>
           <t>35.71428571428575</t>
@@ -9943,12 +9943,12 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>11.90476190476192</t>
+          <t>23.80952380952384</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
@@ -9958,27 +9958,27 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>538.4</t>
+          <t>469.4</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>460.3</t>
+          <t>423.4</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>-148.1662574522824</t>
+          <t>-149.6403341951938</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>-136.44</t>
+          <t>-157.75</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>11.54</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
@@ -10058,12 +10058,12 @@
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
@@ -10095,12 +10095,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -10125,162 +10125,162 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>-1.79</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>-4.25</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>58.04</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>60.614</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>-1.07</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>-1.07</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>35.71428571428575</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>11.90476190476192</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>16.97</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>-0.95</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>-1.98</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>-4.16</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>57.04000000000001</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>58.19</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>60.716</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>-2.99</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>-1.11</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>-15.64</t>
-        </is>
-      </c>
-      <c r="AG33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>453.2</t>
+          <t>538.4</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>537.2</t>
+          <t>460.3</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>-84</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>-150.299019623976</t>
+          <t>-148.1662574522824</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>-146.65</t>
+          <t>-136.44</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
@@ -10330,12 +10330,12 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
@@ -10345,7 +10345,7 @@
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>11.54</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -10412,12 +10412,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -10427,17 +10427,17 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -10467,7 +10467,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -10487,52 +10487,52 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>6</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>57.27999999999999</t>
+          <t>57.04000000000001</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>58.38</t>
+          <t>58.19</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>60.826</t>
+          <t>60.716</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -10547,12 +10547,12 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>8.333333333333337</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>-55.96</t>
+          <t>-15.64</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
@@ -10562,27 +10562,27 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>378.6</t>
+          <t>453.2</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>859.7</t>
+          <t>537.2</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>-481</t>
+          <t>-84</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>-150.9617885310265</t>
+          <t>-150.299019623976</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>-162.98</t>
+          <t>-146.65</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -10607,7 +10607,7 @@
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>11.54</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
@@ -10662,12 +10662,12 @@
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
@@ -10704,7 +10704,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -10729,17 +10729,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -10769,7 +10769,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -10789,47 +10789,47 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>6</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>57.48</t>
+          <t>57.27999999999999</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>58.535</t>
+          <t>58.38</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>60.924</t>
+          <t>60.826</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>-65.36</t>
+          <t>-55.96</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
@@ -10864,27 +10864,27 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>303.2</t>
+          <t>378.6</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>875.2</t>
+          <t>859.7</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>-572</t>
+          <t>-481</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>-148.7771698727741</t>
+          <t>-150.9617885310265</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>-176.94</t>
+          <t>-162.98</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
@@ -10939,7 +10939,7 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>11.54</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
@@ -11006,7 +11006,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -11091,52 +11091,52 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>6</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>57.64</t>
+          <t>57.48</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>58.69000000000001</t>
+          <t>58.535</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>61.018</t>
+          <t>60.924</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -11146,7 +11146,7 @@
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>-54.30</t>
+          <t>-65.36</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
@@ -11166,27 +11166,27 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>377.4</t>
+          <t>303.2</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>825.8</t>
+          <t>875.2</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>-448</t>
+          <t>-572</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>-143.6566541240782</t>
+          <t>-148.7771698727741</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>-209.64</t>
+          <t>-176.94</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
@@ -11236,12 +11236,12 @@
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>11.54</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -11318,12 +11318,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -11353,7 +11353,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -11393,52 +11393,52 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>6</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>-1.79</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>-3.82</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>57.64</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>58.69000000000001</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>61.018</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
           <t>-0.90</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>-1.90</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>-3.68</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>57.72000000000001</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>58.84</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>61.08600000000001</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -11448,17 +11448,17 @@
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>3.030303030303074</t>
+          <t>8.333333333333337</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>-52.09</t>
+          <t>-54.30</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
@@ -11468,27 +11468,27 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>382.2</t>
+          <t>377.4</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>797.8</t>
+          <t>825.8</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>-415</t>
+          <t>-448</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>-131.6598588426528</t>
+          <t>-143.6566541240782</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>-217.79</t>
+          <t>-209.64</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
@@ -11538,12 +11538,12 @@
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>11.54</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="BD37" t="inlineStr">

--- a/Result/checksun/農業科技業.xlsx
+++ b/Result/checksun/農業科技業.xlsx
@@ -1011,15 +1011,11 @@
           <t>20.5625</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>22.51899999999999</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>22.155625</t>
-        </is>
+      <c r="AN2" t="n">
+        <v>22.51899999999999</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>22.155625</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
@@ -1398,15 +1394,11 @@
           <t>20.6075</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>22.594</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>22.150625</t>
-        </is>
+      <c r="AN3" t="n">
+        <v>22.594</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>22.150625</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
@@ -1785,15 +1777,11 @@
           <t>20.695</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>22.652</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>22.135</t>
-        </is>
+      <c r="AN4" t="n">
+        <v>22.652</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>22.135</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
@@ -2172,15 +2160,11 @@
           <t>20.795</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>22.701</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>22.116875</t>
-        </is>
+      <c r="AN5" t="n">
+        <v>22.701</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>22.116875</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
@@ -2559,15 +2543,11 @@
           <t>20.8925</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>22.746</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>22.09625</t>
-        </is>
+      <c r="AN6" t="n">
+        <v>22.746</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>22.09625</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
@@ -2946,15 +2926,11 @@
           <t>20.965</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>22.78</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>22.064375</t>
-        </is>
+      <c r="AN7" t="n">
+        <v>22.78</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>22.064375</v>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
@@ -3333,15 +3309,11 @@
           <t>21.0425</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>22.806</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>22.03375</t>
-        </is>
+      <c r="AN8" t="n">
+        <v>22.806</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>22.03375</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
@@ -3720,15 +3692,11 @@
           <t>21.2025</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>22.86</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>22.0075</t>
-        </is>
+      <c r="AN9" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>22.0075</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
@@ -4107,15 +4075,11 @@
           <t>21.3425</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>22.927</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>21.98125</t>
-        </is>
+      <c r="AN10" t="n">
+        <v>22.927</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>21.98125</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
@@ -4494,15 +4458,11 @@
           <t>21.475</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>22.981</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>21.953125</t>
-        </is>
+      <c r="AN11" t="n">
+        <v>22.981</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>21.953125</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
@@ -4881,15 +4841,11 @@
           <t>24.5025</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>24.864</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>25.535</t>
-        </is>
+      <c r="AN12" t="n">
+        <v>24.864</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>25.535</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
@@ -5268,15 +5224,11 @@
           <t>24.5125</t>
         </is>
       </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>24.887</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>25.573125</t>
-        </is>
+      <c r="AN13" t="n">
+        <v>24.887</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>25.573125</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
@@ -5655,15 +5607,11 @@
           <t>24.5125</t>
         </is>
       </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>24.906</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>25.60875</t>
-        </is>
+      <c r="AN14" t="n">
+        <v>24.906</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>25.60875</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
@@ -6042,15 +5990,11 @@
           <t>24.5</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>24.925</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>25.645625</t>
-        </is>
+      <c r="AN15" t="n">
+        <v>24.925</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>25.645625</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
@@ -6429,15 +6373,11 @@
           <t>24.475</t>
         </is>
       </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>24.942</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>25.67875</t>
-        </is>
+      <c r="AN16" t="n">
+        <v>24.942</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>25.67875</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
@@ -6816,15 +6756,11 @@
           <t>24.45</t>
         </is>
       </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>24.969</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>25.70875</t>
-        </is>
+      <c r="AN17" t="n">
+        <v>24.969</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>25.70875</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
@@ -7203,15 +7139,11 @@
           <t>24.4125</t>
         </is>
       </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>24.994</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>25.735</t>
-        </is>
+      <c r="AN18" t="n">
+        <v>24.994</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>25.735</v>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
@@ -7590,15 +7522,11 @@
           <t>24.41</t>
         </is>
       </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>25.042</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>25.77</t>
-        </is>
+      <c r="AN19" t="n">
+        <v>25.042</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>25.77</v>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
@@ -7977,15 +7905,11 @@
           <t>24.43</t>
         </is>
       </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>25.097</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>25.809375</t>
-        </is>
+      <c r="AN20" t="n">
+        <v>25.097</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>25.809375</v>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
@@ -8364,15 +8288,11 @@
           <t>24.445</t>
         </is>
       </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>25.151</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>25.848125</t>
-        </is>
+      <c r="AN21" t="n">
+        <v>25.151</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>25.848125</v>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
@@ -8751,15 +8671,11 @@
           <t>19.42</t>
         </is>
       </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>19.211</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>19.506875</t>
-        </is>
+      <c r="AN22" t="n">
+        <v>19.211</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>19.506875</v>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
@@ -9138,15 +9054,11 @@
           <t>19.09</t>
         </is>
       </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>19.117</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>19.4525</t>
-        </is>
+      <c r="AN23" t="n">
+        <v>19.117</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>19.4525</v>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
@@ -9525,15 +9437,11 @@
           <t>18.795</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>19.037</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>19.40875</t>
-        </is>
+      <c r="AN24" t="n">
+        <v>19.037</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>19.40875</v>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
@@ -9912,15 +9820,11 @@
           <t>18.375</t>
         </is>
       </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>18.903</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>19.3375</t>
-        </is>
+      <c r="AN25" t="n">
+        <v>18.903</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>19.3375</v>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
@@ -10299,15 +10203,11 @@
           <t>18.03</t>
         </is>
       </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>18.798</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>19.28375</t>
-        </is>
+      <c r="AN26" t="n">
+        <v>18.798</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>19.28375</v>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
@@ -10686,15 +10586,11 @@
           <t>17.8025</t>
         </is>
       </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>18.739</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>19.25875</t>
-        </is>
+      <c r="AN27" t="n">
+        <v>18.739</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>19.25875</v>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
@@ -11073,15 +10969,11 @@
           <t>17.6775</t>
         </is>
       </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>18.72</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>19.261875</t>
-        </is>
+      <c r="AN28" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>19.261875</v>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
@@ -11460,15 +11352,11 @@
           <t>17.6475</t>
         </is>
       </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>18.747</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>19.28875</t>
-        </is>
+      <c r="AN29" t="n">
+        <v>18.747</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>19.28875</v>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
@@ -11847,15 +11735,11 @@
           <t>17.7</t>
         </is>
       </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>18.802</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>19.333125</t>
-        </is>
+      <c r="AN30" t="n">
+        <v>18.802</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>19.333125</v>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
@@ -12234,15 +12118,11 @@
           <t>17.755</t>
         </is>
       </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>18.864</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>19.375625</t>
-        </is>
+      <c r="AN31" t="n">
+        <v>18.864</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>19.375625</v>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
@@ -12621,15 +12501,11 @@
           <t>57.625</t>
         </is>
       </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>59.36799999999999</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>60.50625</t>
-        </is>
+      <c r="AN32" t="n">
+        <v>59.36799999999999</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>60.50625</v>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
@@ -13008,15 +12884,11 @@
           <t>57.645</t>
         </is>
       </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>59.504</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>60.56124999999999</t>
-        </is>
+      <c r="AN33" t="n">
+        <v>59.504</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>60.56124999999999</v>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
@@ -13395,15 +13267,11 @@
           <t>57.67999999999999</t>
         </is>
       </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>59.63799999999999</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>60.62125</t>
-        </is>
+      <c r="AN34" t="n">
+        <v>59.63799999999999</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>60.62125</v>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
@@ -13782,15 +13650,11 @@
           <t>57.70999999999999</t>
         </is>
       </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>59.758</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>60.68125</t>
-        </is>
+      <c r="AN35" t="n">
+        <v>59.758</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>60.68125</v>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
@@ -14169,15 +14033,11 @@
           <t>57.71999999999999</t>
         </is>
       </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>59.86</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>60.73375</t>
-        </is>
+      <c r="AN36" t="n">
+        <v>59.86</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>60.73375</v>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
@@ -14556,15 +14416,11 @@
           <t>57.67999999999999</t>
         </is>
       </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>59.942</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>60.76875</t>
-        </is>
+      <c r="AN37" t="n">
+        <v>59.942</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>60.76875</v>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
@@ -14943,15 +14799,11 @@
           <t>57.56999999999999</t>
         </is>
       </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>59.972</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>60.79</t>
-        </is>
+      <c r="AN38" t="n">
+        <v>59.972</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>60.79</v>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
@@ -15330,15 +15182,11 @@
           <t>57.38500000000001</t>
         </is>
       </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>59.952</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>60.77124999999999</t>
-        </is>
+      <c r="AN39" t="n">
+        <v>59.952</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>60.77124999999999</v>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
@@ -15717,15 +15565,11 @@
           <t>57.485</t>
         </is>
       </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>60.05399999999999</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>60.81875</t>
-        </is>
+      <c r="AN40" t="n">
+        <v>60.05399999999999</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>60.81875</v>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
@@ -16104,15 +15948,11 @@
           <t>57.525</t>
         </is>
       </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>60.14</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>60.855</t>
-        </is>
+      <c r="AN41" t="n">
+        <v>60.14</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>60.855</v>
       </c>
       <c r="AP41" t="inlineStr">
         <is>

--- a/Result/checksun/農業科技業.xlsx
+++ b/Result/checksun/農業科技業.xlsx
@@ -871,7 +871,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>6578</t>
@@ -1293,7 +1297,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>6578</t>
@@ -1715,7 +1723,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>6578</t>
@@ -2137,7 +2149,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>6578</t>
@@ -2559,7 +2575,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>6578</t>
@@ -2981,7 +3001,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>6578</t>
@@ -3403,7 +3427,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>6578</t>
@@ -3825,7 +3853,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>6578</t>
@@ -5527,7 +5559,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5955,7 +5987,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6383,7 +6415,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6811,7 +6843,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7237,7 +7269,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>6508</t>
@@ -7661,7 +7697,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>6508</t>
@@ -8085,7 +8125,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>6508</t>
@@ -16198,7 +16242,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16624,7 +16668,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17050,7 +17094,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17476,7 +17520,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -17902,7 +17946,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18328,7 +18372,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18754,7 +18798,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19180,7 +19224,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
